--- a/avito_catalog.xlsx
+++ b/avito_catalog.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Справочники" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Каталог'!$A$1:$P$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Каталог'!$A$1:$Q$500</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -535,78 +535,92 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3. Зелёные колонки ЦЕНА ОТ / ЦЕНА ДО = ценовой диапазон для этой модели. Пусто = без ограничения.</t>
+          <t xml:space="preserve">   «Вариант»: если у модели есть версии (RTX 4060 Ti 8GB и 16GB), сделай по строке на версию с одинаковой «Моделью».</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4. Чтобы добавить модель, скопируй похожую строку и поменяй «Модель», цену и «Поисковый запрос». Новая кнопка появится в боте сама.</t>
+          <t xml:space="preserve">   В боте будет одна кнопка RTX 4060 Ti, но каждая версия ищется со своей ценой. Объём памяти впиши и в «Обязательные слова».</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5. «Вкл» = нет: строка остаётся в таблице, но бот её не показывает и парсер её не ищет.</t>
+          <t>3. Зелёные колонки ЦЕНА ОТ / ЦЕНА ДО = ценовой диапазон для этой модели. Пусто = без ограничения.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6. Только исправное: общий список стоп-слов (не работает, артефакты, на запчасти…) лежит на листе «Настройки» и применяется ко всем строкам.</t>
+          <t>4. Чтобы добавить модель, скопируй похожую строку и поменяй «Модель», цену и «Поисковый запрос». Новая кнопка появится в боте сама.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   В колонке «Минус-слова (доп.)» пиши только то, что нужно конкретной модели. Например у «RTX 4060» стоит «Ti», иначе в выдачу попадут 4060 Ti.</t>
+          <t>5. «Вкл» = нет: строка остаётся в таблице, но бот её не показывает и парсер её не ищет.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>7. «Обязательные слова» через запятую: в заголовке должны быть все эти слова (например «12» для RTX 3060 12GB).</t>
+          <t>6. Только исправное: общий список стоп-слов (не работает, артефакты, на запчасти…) лежит на листе «Настройки» и применяется ко всем строкам.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>8. Жёлтые колонки необязательны. Пустая ячейка = значение по умолчанию с листа «Настройки» (Санкт-Петербург + 50 км, б/у).</t>
+          <t xml:space="preserve">   В колонке «Минус-слова (доп.)» пиши только то, что нужно конкретной модели. Например у «RTX 4060» стоит «Ti», иначе в выдачу попадут 4060 Ti.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>9. Названия разделов пиши одинаково во всех строках (NVIDIA, а не Nvidia), иначе в боте будет две кнопки.</t>
+          <t>7. «Обязательные слова» через запятую: в заголовке должны быть все эти слова (например «12» для RTX 3060 12GB).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10. Выпадающие списки берут значения с листа «Справочники», туда можно дописывать свои.</t>
+          <t>8. Жёлтые колонки необязательны. Пустая ячейка = значение по умолчанию с листа «Настройки» (Санкт-Петербург + 50 км, б/у). Объявления из других регионов бот отбрасывает.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>9. Названия разделов пиши одинаково во всех строках (NVIDIA, а не Nvidia), иначе в боте будет две кнопки.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Цены в строках RTX 4060 / 4060 Ti стоят для примера, поставьте свои.</t>
+          <t>10. Выпадающие списки берут значения с листа «Справочники», туда можно дописывать свои.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Цены в строках RTX 4060 / 4060 Ti (8GB и 16GB) стоят для примера, поставьте свои.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Google Таблицы: Файл → Импорт → Загрузить этот файл → «Заменить таблицу», затем «Настройки доступа» и добавить напарника как редактора.</t>
         </is>
@@ -623,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P500"/>
+  <dimension ref="A1:Q500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -631,17 +645,18 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -677,50 +692,55 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
           <t>Вкл</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>ЦЕНА ОТ, ₽</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ЦЕНА ДО, ₽</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Поисковый запрос</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Обязательные слова</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Минус-слова (доп.)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Состояние</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Только с доставкой</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -753,28 +773,29 @@
           <t>GTX 1060 6GB</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>GTX 1060</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr"/>
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>ноутбук, 3GB, 3 GB, 3Гб</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
       <c r="N2" s="9" t="inlineStr"/>
       <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="7" t="inlineStr"/>
+      <c r="P2" s="9" t="inlineStr"/>
+      <c r="Q2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -803,28 +824,29 @@
           <t>GTX 1070</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="8" t="n"/>
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>GTX 1070</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr"/>
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>ноутбук, Ti</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
       <c r="N3" s="9" t="inlineStr"/>
       <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="7" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr"/>
+      <c r="Q3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -853,32 +875,33 @@
           <t>GTX 1080 Ti</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>GTX 1080 Ti</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Ti</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr"/>
       <c r="N4" s="9" t="inlineStr"/>
       <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="7" t="inlineStr"/>
+      <c r="P4" s="9" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -907,28 +930,29 @@
           <t>GTX 1650</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>GTX 1650</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr"/>
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>ноутбук, Super</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr"/>
       <c r="N5" s="9" t="inlineStr"/>
       <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="7" t="inlineStr"/>
+      <c r="P5" s="9" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -957,32 +981,33 @@
           <t>GTX 1660 Super</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H6" s="8" t="n"/>
       <c r="I6" s="8" t="n"/>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>GTX 1660 Super</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
       <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="7" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1011,32 +1036,33 @@
           <t>GTX 1660 Ti</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>GTX 1660 Ti</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Ti</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr"/>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="9" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1065,28 +1091,29 @@
           <t>RTX 2060</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>RTX 2060</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>ноутбук, Super</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr"/>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="9" t="inlineStr"/>
-      <c r="P8" s="7" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1115,32 +1142,33 @@
           <t>RTX 2060 Super</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>RTX 2060 Super</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr"/>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="9" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1169,32 +1197,33 @@
           <t>RTX 2070 Super</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>RTX 2070 Super</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr"/>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="9" t="inlineStr"/>
-      <c r="P10" s="7" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1223,32 +1252,33 @@
           <t>RTX 2080 Ti</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>RTX 2080 Ti</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>Ti</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M11" s="9" t="inlineStr"/>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="9" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1278,35 +1308,40 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+          <t>RTX 3060</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>RTX 3060</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti, 8GB</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr"/>
+          <t>12GB</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="9" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1336,35 +1371,40 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>RTX 3060 Ti</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
+          <t>RTX 3060</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H13" s="8" t="n"/>
       <c r="I13" s="8" t="n"/>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>RTX 3060 Ti</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="n"/>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>RTX 3060</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr"/>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N13" s="9" t="inlineStr"/>
       <c r="O13" s="9" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
+      <c r="P13" s="9" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1389,36 +1429,41 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>RTX 3070</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+          <t>RTX 3060 Ti</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>RTX 3070</t>
-        </is>
-      </c>
-      <c r="K14" s="9" t="inlineStr"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>RTX 3060 Ti</t>
+        </is>
+      </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr"/>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N14" s="9" t="inlineStr"/>
       <c r="O14" s="9" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr"/>
+      <c r="P14" s="9" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1448,35 +1493,32 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>RTX 3070 Ti</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
+          <t>RTX 3070</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>RTX 3070 Ti</t>
-        </is>
-      </c>
+      <c r="J15" s="8" t="n"/>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr"/>
+          <t>RTX 3070</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr"/>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N15" s="9" t="inlineStr"/>
       <c r="O15" s="9" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
+      <c r="P15" s="9" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1501,36 +1543,41 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>RTX 3080</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+          <t>RTX 3070 Ti</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>RTX 3080</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>RTX 3070 Ti</t>
+        </is>
+      </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr"/>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N16" s="9" t="inlineStr"/>
       <c r="O16" s="9" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr"/>
+      <c r="P16" s="9" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1550,49 +1597,42 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>RTX 4060</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
+          <t>RTX 3080</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4060</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>RTX 3080</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>ноутбук, Ti</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr"/>
       <c r="N17" s="9" t="inlineStr"/>
       <c r="O17" s="9" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>Ветка со схемы. Цены для примера</t>
-        </is>
-      </c>
+      <c r="P17" s="9" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1622,39 +1662,36 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>RTX 4060 Ti</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
+          <t>RTX 4060</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>20000</v>
-      </c>
       <c r="I18" s="8" t="n">
-        <v>33000</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4060 Ti</t>
-        </is>
+        <v>15000</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>25000</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Ti</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr"/>
+          <t>RTX 4060</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N18" s="9" t="inlineStr"/>
       <c r="O18" s="9" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="P18" s="9" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>Ветка со схемы. Цены для примера</t>
         </is>
@@ -1683,36 +1720,53 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>RTX 4070</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
+          <t>RTX 4060 Ti</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4070</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr"/>
+      <c r="I19" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>RTX 4060 Ti</t>
+        </is>
+      </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti, Super</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr"/>
+          <t>Ti, 8GB</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N19" s="9" t="inlineStr"/>
       <c r="O19" s="9" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr"/>
+      <c r="P19" s="9" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>Версии: одна кнопка в боте, свои цены</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1737,40 +1791,53 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>RTX 4070 Super</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+          <t>RTX 4060 Ti</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4070 Super</t>
-        </is>
+      <c r="I20" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>35000</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Super</t>
+          <t>RTX 4060 Ti</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr"/>
+          <t>Ti, 16GB</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N20" s="9" t="inlineStr"/>
       <c r="O20" s="9" t="inlineStr"/>
-      <c r="P20" s="7" t="inlineStr"/>
+      <c r="P20" s="9" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>Версии: одна кнопка в боте, свои цены</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1800,35 +1867,32 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>RTX 4070 Ti Super</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
+          <t>RTX 4070</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4070 Ti Super</t>
-        </is>
-      </c>
+      <c r="J21" s="8" t="n"/>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Ti, Super</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr"/>
+          <t>RTX 4070</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr"/>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti, Super</t>
+        </is>
+      </c>
       <c r="N21" s="9" t="inlineStr"/>
       <c r="O21" s="9" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr"/>
+      <c r="P21" s="9" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1853,40 +1917,41 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>RTX 4080 Super</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
+          <t>RTX 4070 Super</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>RTX 4080 Super</t>
-        </is>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
+          <t>RTX 4070 Super</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
           <t>Super</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M22" s="9" t="inlineStr"/>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N22" s="9" t="inlineStr"/>
       <c r="O22" s="9" t="inlineStr"/>
-      <c r="P22" s="7" t="inlineStr"/>
+      <c r="P22" s="9" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1906,41 +1971,46 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>4070</t>
+        </is>
+      </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>RTX 5060 Ti</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
+          <t>RTX 4070 Ti Super</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H23" s="8" t="n"/>
       <c r="I23" s="8" t="n"/>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060 Ti</t>
-        </is>
-      </c>
+      <c r="J23" s="8" t="n"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>RTX 4070 Ti Super</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
+          <t>Ti, Super</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr"/>
       <c r="O23" s="9" t="inlineStr"/>
-      <c r="P23" s="7" t="inlineStr"/>
+      <c r="P23" s="9" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1960,37 +2030,46 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>4080</t>
+        </is>
+      </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
+          <t>RTX 4080 Super</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>RTX 4080 Super</t>
+        </is>
+      </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, Ti</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr"/>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N24" s="9" t="inlineStr"/>
       <c r="O24" s="9" t="inlineStr"/>
-      <c r="P24" s="7" t="inlineStr"/>
+      <c r="P24" s="9" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2016,35 +2095,40 @@
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>RTX 5070 Ti</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+          <t>RTX 5060 Ti</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>8GB</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H25" s="8" t="n"/>
       <c r="I25" s="8" t="n"/>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070 Ti</t>
-        </is>
-      </c>
+      <c r="J25" s="8" t="n"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Ti</t>
+          <t>RTX 5060 Ti</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
+          <t>Ti, 8GB</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M25" s="9" t="inlineStr"/>
       <c r="N25" s="9" t="inlineStr"/>
       <c r="O25" s="9" t="inlineStr"/>
-      <c r="P25" s="7" t="inlineStr"/>
+      <c r="P25" s="9" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2054,47 +2138,56 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>RX 6600</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
+          <t>RTX 5060 Ti</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>16GB</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>RX 6600</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="inlineStr"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060 Ti</t>
+        </is>
+      </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, XT</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr"/>
+          <t>Ti, 16GB</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N26" s="9" t="inlineStr"/>
       <c r="O26" s="9" t="inlineStr"/>
-      <c r="P26" s="7" t="inlineStr"/>
+      <c r="P26" s="9" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2104,51 +2197,48 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>RX 6700 XT</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n"/>
       <c r="I27" s="8" t="n"/>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>RX 6700 XT</t>
-        </is>
-      </c>
+      <c r="J27" s="8" t="n"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>XT</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="inlineStr"/>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, Ti</t>
+        </is>
+      </c>
       <c r="N27" s="9" t="inlineStr"/>
       <c r="O27" s="9" t="inlineStr"/>
-      <c r="P27" s="7" t="inlineStr"/>
+      <c r="P27" s="9" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2158,47 +2248,52 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>RX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>RX 6800</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
+          <t>RTX 5070 Ti</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>RX 6800</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070 Ti</t>
+        </is>
+      </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, XT</t>
-        </is>
-      </c>
-      <c r="M28" s="9" t="inlineStr"/>
+          <t>Ti</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N28" s="9" t="inlineStr"/>
       <c r="O28" s="9" t="inlineStr"/>
-      <c r="P28" s="7" t="inlineStr"/>
+      <c r="P28" s="9" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2218,37 +2313,38 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>RX 7600</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+          <t>RX 6600</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>RX 7600</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>RX 6600</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr"/>
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>ноутбук, XT</t>
         </is>
       </c>
-      <c r="M29" s="9" t="inlineStr"/>
       <c r="N29" s="9" t="inlineStr"/>
       <c r="O29" s="9" t="inlineStr"/>
-      <c r="P29" s="7" t="inlineStr"/>
+      <c r="P29" s="9" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2268,41 +2364,42 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>RX 7700 XT</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
+          <t>RX 6700 XT</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H30" s="8" t="n"/>
       <c r="I30" s="8" t="n"/>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>RX 7700 XT</t>
-        </is>
-      </c>
+      <c r="J30" s="8" t="n"/>
       <c r="K30" s="9" t="inlineStr">
         <is>
+          <t>RX 6700 XT</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
           <t>XT</t>
         </is>
       </c>
-      <c r="L30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M30" s="9" t="inlineStr"/>
       <c r="N30" s="9" t="inlineStr"/>
       <c r="O30" s="9" t="inlineStr"/>
-      <c r="P30" s="7" t="inlineStr"/>
+      <c r="P30" s="9" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2322,41 +2419,38 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>RX 7800 XT</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
+          <t>RX 6800</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H31" s="8" t="n"/>
       <c r="I31" s="8" t="n"/>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>RX 7800 XT</t>
-        </is>
-      </c>
+      <c r="J31" s="8" t="n"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>XT</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr"/>
+          <t>RX 6800</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, XT</t>
+        </is>
+      </c>
       <c r="N31" s="9" t="inlineStr"/>
       <c r="O31" s="9" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr"/>
+      <c r="P31" s="9" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2376,41 +2470,38 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>RX 9060 XT</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
+          <t>RX 7600</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H32" s="8" t="n"/>
       <c r="I32" s="8" t="n"/>
-      <c r="J32" s="9" t="inlineStr">
-        <is>
-          <t>RX 9060 XT</t>
-        </is>
-      </c>
+      <c r="J32" s="8" t="n"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>XT</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>ноутбук</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr"/>
+          <t>RX 7600</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, XT</t>
+        </is>
+      </c>
       <c r="N32" s="9" t="inlineStr"/>
       <c r="O32" s="9" t="inlineStr"/>
-      <c r="P32" s="7" t="inlineStr"/>
+      <c r="P32" s="9" t="inlineStr"/>
+      <c r="Q32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2430,203 +2521,207 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>RX 9070 XT</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+          <t>RX 7700 XT</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H33" s="8" t="n"/>
       <c r="I33" s="8" t="n"/>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>RX 9070 XT</t>
-        </is>
-      </c>
+      <c r="J33" s="8" t="n"/>
       <c r="K33" s="9" t="inlineStr">
         <is>
+          <t>RX 7700 XT</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
           <t>XT</t>
         </is>
       </c>
-      <c r="L33" s="9" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>ноутбук</t>
         </is>
       </c>
-      <c r="M33" s="9" t="inlineStr"/>
       <c r="N33" s="9" t="inlineStr"/>
       <c r="O33" s="9" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr"/>
+      <c r="P33" s="9" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Процессоры</t>
+          <t>Видеокарты</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Core i5</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>12-е пок.</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>i5-12400F</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
+          <t>RX 7800 XT</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H34" s="8" t="n"/>
       <c r="I34" s="8" t="n"/>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>i5 12400F</t>
-        </is>
-      </c>
+      <c r="J34" s="8" t="n"/>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>12400</t>
+          <t>RX 7800 XT</t>
         </is>
       </c>
       <c r="L34" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный</t>
-        </is>
-      </c>
-      <c r="M34" s="9" t="inlineStr"/>
+          <t>XT</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N34" s="9" t="inlineStr"/>
       <c r="O34" s="9" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr"/>
+      <c r="P34" s="9" t="inlineStr"/>
+      <c r="Q34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Процессоры</t>
+          <t>Видеокарты</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Core i5</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>12-е пок.</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>i5-12600K</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
+          <t>RX 9060 XT</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H35" s="8" t="n"/>
       <c r="I35" s="8" t="n"/>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>i5 12600K</t>
-        </is>
-      </c>
+      <c r="J35" s="8" t="n"/>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>RX 9060 XT</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный, KF</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="inlineStr"/>
+          <t>XT</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N35" s="9" t="inlineStr"/>
       <c r="O35" s="9" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr"/>
+      <c r="P35" s="9" t="inlineStr"/>
+      <c r="Q35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Процессоры</t>
+          <t>Видеокарты</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Core i5</t>
+          <t>RX</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>13-14 пок.</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>i5-13400F</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
+          <t>RX 9070 XT</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H36" s="8" t="n"/>
       <c r="I36" s="8" t="n"/>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>i5 13400F</t>
-        </is>
-      </c>
+      <c r="J36" s="8" t="n"/>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>RX 9070 XT</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный</t>
-        </is>
-      </c>
-      <c r="M36" s="9" t="inlineStr"/>
+          <t>XT</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук</t>
+        </is>
+      </c>
       <c r="N36" s="9" t="inlineStr"/>
       <c r="O36" s="9" t="inlineStr"/>
-      <c r="P36" s="7" t="inlineStr"/>
+      <c r="P36" s="9" t="inlineStr"/>
+      <c r="Q36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2646,41 +2741,42 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>13-14 пок.</t>
+          <t>12-е пок.</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>i5-14600KF</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
+          <t>i5-12400F</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H37" s="8" t="n"/>
       <c r="I37" s="8" t="n"/>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>i5 14600KF</t>
-        </is>
-      </c>
+      <c r="J37" s="8" t="n"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>i5 12400F</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
+          <t>12400</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr"/>
       <c r="N37" s="9" t="inlineStr"/>
       <c r="O37" s="9" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr"/>
+      <c r="P37" s="9" t="inlineStr"/>
+      <c r="Q37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2695,7 +2791,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Core i7</t>
+          <t>Core i5</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2706,35 +2802,36 @@
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>i7-12700K</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
+          <t>i5-12600K</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H38" s="8" t="n"/>
       <c r="I38" s="8" t="n"/>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>i7 12700K</t>
-        </is>
-      </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>i5 12600K</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный, KF</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr"/>
       <c r="N38" s="9" t="inlineStr"/>
       <c r="O38" s="9" t="inlineStr"/>
-      <c r="P38" s="7" t="inlineStr"/>
+      <c r="P38" s="9" t="inlineStr"/>
+      <c r="Q38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2749,7 +2846,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Core i7</t>
+          <t>Core i5</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2760,35 +2857,36 @@
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>i7-14700K</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
+          <t>i5-13400F</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>i7 14700K</t>
-        </is>
-      </c>
+      <c r="J39" s="8" t="n"/>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>i5 13400F</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
+          <t>13400</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr"/>
       <c r="N39" s="9" t="inlineStr"/>
       <c r="O39" s="9" t="inlineStr"/>
-      <c r="P39" s="7" t="inlineStr"/>
+      <c r="P39" s="9" t="inlineStr"/>
+      <c r="Q39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2798,51 +2896,52 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5</t>
+          <t>Core i5</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AM4</t>
+          <t>13-14 пок.</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
+          <t>i5-14600KF</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H40" s="8" t="n"/>
       <c r="I40" s="8" t="n"/>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 5 5600</t>
-        </is>
-      </c>
+      <c r="J40" s="8" t="n"/>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>i5 14600KF</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный, 5600X, 5600G</t>
-        </is>
-      </c>
-      <c r="M40" s="9" t="inlineStr"/>
+          <t>14600</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный</t>
+        </is>
+      </c>
       <c r="N40" s="9" t="inlineStr"/>
       <c r="O40" s="9" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr"/>
+      <c r="P40" s="9" t="inlineStr"/>
+      <c r="Q40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2852,51 +2951,52 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5</t>
+          <t>Core i7</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>AM4</t>
+          <t>12-е пок.</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600X</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
+          <t>i7-12700K</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n"/>
       <c r="I41" s="8" t="n"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 5 5600X</t>
-        </is>
-      </c>
+      <c r="J41" s="8" t="n"/>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>5600X</t>
+          <t>i7 12700K</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="inlineStr"/>
+          <t>12700</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный, KF</t>
+        </is>
+      </c>
       <c r="N41" s="9" t="inlineStr"/>
       <c r="O41" s="9" t="inlineStr"/>
-      <c r="P41" s="7" t="inlineStr"/>
+      <c r="P41" s="9" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2906,51 +3006,52 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5</t>
+          <t>Core i7</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>AM5</t>
+          <t>13-14 пок.</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 5 7500F</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
+          <t>i7-14700K</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H42" s="8" t="n"/>
       <c r="I42" s="8" t="n"/>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 5 7500F</t>
-        </is>
-      </c>
+      <c r="J42" s="8" t="n"/>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>7500F</t>
+          <t>i7 14700K</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
+          <t>14700</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr"/>
       <c r="N42" s="9" t="inlineStr"/>
       <c r="O42" s="9" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr"/>
+      <c r="P42" s="9" t="inlineStr"/>
+      <c r="Q42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2970,41 +3071,42 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>AM5</t>
+          <t>AM4</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H43" s="8" t="n"/>
       <c r="I43" s="8" t="n"/>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 5 7600</t>
-        </is>
-      </c>
+      <c r="J43" s="8" t="n"/>
       <c r="K43" s="9" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный, 7600X</t>
-        </is>
-      </c>
-      <c r="M43" s="9" t="inlineStr"/>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный, 5600X, 5600G</t>
+        </is>
+      </c>
       <c r="N43" s="9" t="inlineStr"/>
       <c r="O43" s="9" t="inlineStr"/>
-      <c r="P43" s="7" t="inlineStr"/>
+      <c r="P43" s="9" t="inlineStr"/>
+      <c r="Q43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3019,7 +3121,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7</t>
+          <t>Ryzen 5</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3030,35 +3132,36 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
+          <t>Ryzen 5 5600X</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H44" s="8" t="n"/>
       <c r="I44" s="8" t="n"/>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 7 5700X3D</t>
-        </is>
-      </c>
+      <c r="J44" s="8" t="n"/>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>5700X3D</t>
+          <t>Ryzen 5 5600X</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
+          <t>5600X</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="9" t="inlineStr"/>
       <c r="O44" s="9" t="inlineStr"/>
-      <c r="P44" s="7" t="inlineStr"/>
+      <c r="P44" s="9" t="inlineStr"/>
+      <c r="Q44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3073,46 +3176,47 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7</t>
+          <t>Ryzen 5</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>AM4</t>
+          <t>AM5</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 7 5800X3D</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
+          <t>Ryzen 5 7500F</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H45" s="8" t="n"/>
       <c r="I45" s="8" t="n"/>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 7 5800X3D</t>
-        </is>
-      </c>
+      <c r="J45" s="8" t="n"/>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>5800X3D</t>
+          <t>Ryzen 5 7500F</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
+          <t>7500F</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr"/>
       <c r="N45" s="9" t="inlineStr"/>
       <c r="O45" s="9" t="inlineStr"/>
-      <c r="P45" s="7" t="inlineStr"/>
+      <c r="P45" s="9" t="inlineStr"/>
+      <c r="Q45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3127,7 +3231,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7</t>
+          <t>Ryzen 5</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -3138,35 +3242,36 @@
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H46" s="8" t="n"/>
       <c r="I46" s="8" t="n"/>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 7 7800X3D</t>
-        </is>
-      </c>
+      <c r="J46" s="8" t="n"/>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, ES, QS, инженерный</t>
-        </is>
-      </c>
-      <c r="M46" s="9" t="inlineStr"/>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный, 7600X</t>
+        </is>
+      </c>
       <c r="N46" s="9" t="inlineStr"/>
       <c r="O46" s="9" t="inlineStr"/>
-      <c r="P46" s="7" t="inlineStr"/>
+      <c r="P46" s="9" t="inlineStr"/>
+      <c r="Q46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -3186,191 +3291,207 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AM5</t>
+          <t>AM4</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>Ryzen 7 9800X3D</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
+          <t>Ryzen 7 5700X3D</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H47" s="8" t="n"/>
       <c r="I47" s="8" t="n"/>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Ryzen 7 9800X3D</t>
-        </is>
-      </c>
+      <c r="J47" s="8" t="n"/>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>9800X3D</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
+          <t>5700X3D</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, ES, QS, инженерный</t>
         </is>
       </c>
-      <c r="M47" s="9" t="inlineStr"/>
       <c r="N47" s="9" t="inlineStr"/>
       <c r="O47" s="9" t="inlineStr"/>
-      <c r="P47" s="7" t="inlineStr"/>
+      <c r="P47" s="9" t="inlineStr"/>
+      <c r="Q47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Материнки</t>
+          <t>Процессоры</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>LGA1700</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr"/>
+          <t>Ryzen 7</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>AM4</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>B760 DDR4</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
+          <t>Ryzen 7 5800X3D</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H48" s="8" t="n"/>
       <c r="I48" s="8" t="n"/>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата B760 DDR4</t>
-        </is>
-      </c>
+      <c r="J48" s="8" t="n"/>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>B760, DDR4</t>
+          <t>Ryzen 7 5800X3D</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>без заглушки, DDR5</t>
-        </is>
-      </c>
-      <c r="M48" s="9" t="inlineStr"/>
+          <t>5800X3D</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный</t>
+        </is>
+      </c>
       <c r="N48" s="9" t="inlineStr"/>
       <c r="O48" s="9" t="inlineStr"/>
-      <c r="P48" s="7" t="inlineStr"/>
+      <c r="P48" s="9" t="inlineStr"/>
+      <c r="Q48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Материнки</t>
+          <t>Процессоры</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>LGA1700</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr"/>
+          <t>Ryzen 7</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>AM5</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>B760 DDR5</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H49" s="8" t="n"/>
       <c r="I49" s="8" t="n"/>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата B760 DDR5</t>
-        </is>
-      </c>
+      <c r="J49" s="8" t="n"/>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>B760, DDR5</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>без заглушки, DDR4</t>
-        </is>
-      </c>
-      <c r="M49" s="9" t="inlineStr"/>
+          <t>7800X3D</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный</t>
+        </is>
+      </c>
       <c r="N49" s="9" t="inlineStr"/>
       <c r="O49" s="9" t="inlineStr"/>
-      <c r="P49" s="7" t="inlineStr"/>
+      <c r="P49" s="9" t="inlineStr"/>
+      <c r="Q49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Материнки</t>
+          <t>Процессоры</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>LGA1700</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr"/>
+          <t>Ryzen 7</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>AM5</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Z790</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
+          <t>Ryzen 7 9800X3D</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H50" s="8" t="n"/>
       <c r="I50" s="8" t="n"/>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата Z790</t>
-        </is>
-      </c>
+      <c r="J50" s="8" t="n"/>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>Z790</t>
+          <t>Ryzen 7 9800X3D</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>без заглушки</t>
-        </is>
-      </c>
-      <c r="M50" s="9" t="inlineStr"/>
+          <t>9800X3D</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, ES, QS, инженерный</t>
+        </is>
+      </c>
       <c r="N50" s="9" t="inlineStr"/>
       <c r="O50" s="9" t="inlineStr"/>
-      <c r="P50" s="7" t="inlineStr"/>
+      <c r="P50" s="9" t="inlineStr"/>
+      <c r="Q50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3380,47 +3501,48 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>AM4</t>
+          <t>LGA1700</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr"/>
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>B450</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
+          <t>B760 DDR4</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H51" s="8" t="n"/>
       <c r="I51" s="8" t="n"/>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата B450</t>
-        </is>
-      </c>
+      <c r="J51" s="8" t="n"/>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>B450</t>
+          <t>материнская плата B760 DDR4</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>без заглушки</t>
-        </is>
-      </c>
-      <c r="M51" s="9" t="inlineStr"/>
+          <t>B760, DDR4</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>без заглушки, DDR5</t>
+        </is>
+      </c>
       <c r="N51" s="9" t="inlineStr"/>
       <c r="O51" s="9" t="inlineStr"/>
-      <c r="P51" s="7" t="inlineStr"/>
+      <c r="P51" s="9" t="inlineStr"/>
+      <c r="Q51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3430,47 +3552,48 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AM4</t>
+          <t>LGA1700</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr"/>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>B550</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
+          <t>B760 DDR5</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H52" s="8" t="n"/>
       <c r="I52" s="8" t="n"/>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата B550</t>
-        </is>
-      </c>
+      <c r="J52" s="8" t="n"/>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>B550</t>
+          <t>материнская плата B760 DDR5</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>без заглушки</t>
-        </is>
-      </c>
-      <c r="M52" s="9" t="inlineStr"/>
+          <t>B760, DDR5</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>без заглушки, DDR4</t>
+        </is>
+      </c>
       <c r="N52" s="9" t="inlineStr"/>
       <c r="O52" s="9" t="inlineStr"/>
-      <c r="P52" s="7" t="inlineStr"/>
+      <c r="P52" s="9" t="inlineStr"/>
+      <c r="Q52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3480,47 +3603,48 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>AM5</t>
+          <t>LGA1700</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr"/>
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>B650</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
+          <t>Z790</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H53" s="8" t="n"/>
       <c r="I53" s="8" t="n"/>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата B650</t>
-        </is>
-      </c>
+      <c r="J53" s="8" t="n"/>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>B650</t>
+          <t>материнская плата Z790</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
+          <t>Z790</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
           <t>без заглушки</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr"/>
       <c r="N53" s="9" t="inlineStr"/>
       <c r="O53" s="9" t="inlineStr"/>
-      <c r="P53" s="7" t="inlineStr"/>
+      <c r="P53" s="9" t="inlineStr"/>
+      <c r="Q53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3535,192 +3659,196 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AM5</t>
+          <t>AM4</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr"/>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>X670</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
+          <t>B450</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H54" s="8" t="n"/>
       <c r="I54" s="8" t="n"/>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>материнская плата X670</t>
-        </is>
-      </c>
+      <c r="J54" s="8" t="n"/>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>X670</t>
+          <t>материнская плата B450</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
+          <t>B450</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
           <t>без заглушки</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr"/>
       <c r="N54" s="9" t="inlineStr"/>
       <c r="O54" s="9" t="inlineStr"/>
-      <c r="P54" s="7" t="inlineStr"/>
+      <c r="P54" s="9" t="inlineStr"/>
+      <c r="Q54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Оперативка</t>
+          <t>Материнки</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DDR4</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>16 ГБ</t>
+          <t>AM4</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr"/>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>DDR4 2x8GB 3200</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
+          <t>B550</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H55" s="8" t="n"/>
       <c r="I55" s="8" t="n"/>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>DDR4 16GB 2x8 3200</t>
-        </is>
-      </c>
+      <c r="J55" s="8" t="n"/>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>DDR4, 3200</t>
+          <t>материнская плата B550</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, SO-DIMM, sodimm</t>
-        </is>
-      </c>
-      <c r="M55" s="9" t="inlineStr"/>
+          <t>B550</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>без заглушки</t>
+        </is>
+      </c>
       <c r="N55" s="9" t="inlineStr"/>
       <c r="O55" s="9" t="inlineStr"/>
-      <c r="P55" s="7" t="inlineStr"/>
+      <c r="P55" s="9" t="inlineStr"/>
+      <c r="Q55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Оперативка</t>
+          <t>Материнки</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>DDR4</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>32 ГБ</t>
+          <t>AM5</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>DDR4 2x16GB 3200</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
+          <t>B650</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H56" s="8" t="n"/>
       <c r="I56" s="8" t="n"/>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>DDR4 32GB 2x16 3200</t>
-        </is>
-      </c>
+      <c r="J56" s="8" t="n"/>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>DDR4</t>
+          <t>материнская плата B650</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, SO-DIMM, sodimm</t>
-        </is>
-      </c>
-      <c r="M56" s="9" t="inlineStr"/>
+          <t>B650</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>без заглушки</t>
+        </is>
+      </c>
       <c r="N56" s="9" t="inlineStr"/>
       <c r="O56" s="9" t="inlineStr"/>
-      <c r="P56" s="7" t="inlineStr"/>
+      <c r="P56" s="9" t="inlineStr"/>
+      <c r="Q56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Оперативка</t>
+          <t>Материнки</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>DDR4</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>32 ГБ</t>
+          <t>AM5</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr"/>
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>DDR4 2x16GB 3600</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr">
+          <t>X670</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H57" s="8" t="n"/>
       <c r="I57" s="8" t="n"/>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>DDR4 32GB 2x16 3600</t>
-        </is>
-      </c>
+      <c r="J57" s="8" t="n"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>DDR4, 3600</t>
+          <t>материнская плата X670</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>ноутбук, SO-DIMM, sodimm</t>
-        </is>
-      </c>
-      <c r="M57" s="9" t="inlineStr"/>
+          <t>X670</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>без заглушки</t>
+        </is>
+      </c>
       <c r="N57" s="9" t="inlineStr"/>
       <c r="O57" s="9" t="inlineStr"/>
-      <c r="P57" s="7" t="inlineStr"/>
+      <c r="P57" s="9" t="inlineStr"/>
+      <c r="Q57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3730,47 +3858,48 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>DDR5</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>32 ГБ</t>
+          <t>16 ГБ</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>DDR5 2x16GB 6000</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
+          <t>DDR4 2x8GB 3200</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H58" s="8" t="n"/>
       <c r="I58" s="8" t="n"/>
-      <c r="J58" s="9" t="inlineStr">
-        <is>
-          <t>DDR5 32GB 2x16 6000</t>
-        </is>
-      </c>
+      <c r="J58" s="8" t="n"/>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>DDR5, 6000</t>
+          <t>DDR4 16GB 2x8 3200</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
+          <t>DDR4, 3200</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, SO-DIMM, sodimm</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr"/>
       <c r="N58" s="9" t="inlineStr"/>
       <c r="O58" s="9" t="inlineStr"/>
-      <c r="P58" s="7" t="inlineStr"/>
+      <c r="P58" s="9" t="inlineStr"/>
+      <c r="Q58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3780,101 +3909,201 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>DDR5</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>64 ГБ</t>
+          <t>32 ГБ</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>DDR5 2x32GB 6000</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
+          <t>DDR4 2x16GB 3200</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="H59" s="8" t="n"/>
       <c r="I59" s="8" t="n"/>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>DDR5 64GB 2x32 6000</t>
-        </is>
-      </c>
+      <c r="J59" s="8" t="n"/>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>DDR5</t>
+          <t>DDR4 32GB 2x16 3200</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
           <t>ноутбук, SO-DIMM, sodimm</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr"/>
       <c r="N59" s="9" t="inlineStr"/>
       <c r="O59" s="9" t="inlineStr"/>
-      <c r="P59" s="7" t="inlineStr"/>
+      <c r="P59" s="9" t="inlineStr"/>
+      <c r="Q59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
-      <c r="F60" s="7" t="n"/>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="7" t="n"/>
-      <c r="I60" s="7" t="n"/>
-      <c r="J60" s="7" t="n"/>
-      <c r="K60" s="7" t="n"/>
-      <c r="L60" s="7" t="n"/>
-      <c r="M60" s="7" t="n"/>
-      <c r="N60" s="7" t="n"/>
-      <c r="O60" s="7" t="n"/>
-      <c r="P60" s="7" t="n"/>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Оперативка</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>32 ГБ</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>DDR4 2x16GB 3600</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>DDR4 32GB 2x16 3600</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>DDR4, 3600</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, SO-DIMM, sodimm</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr"/>
+      <c r="O60" s="9" t="inlineStr"/>
+      <c r="P60" s="9" t="inlineStr"/>
+      <c r="Q60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="7" t="n"/>
-      <c r="K61" s="7" t="n"/>
-      <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
-      <c r="N61" s="7" t="n"/>
-      <c r="O61" s="7" t="n"/>
-      <c r="P61" s="7" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Оперативка</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>DDR5</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>32 ГБ</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 2x16GB 6000</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>DDR5 32GB 2x16 6000</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>DDR5, 6000</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, SO-DIMM, sodimm</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr"/>
+      <c r="O61" s="9" t="inlineStr"/>
+      <c r="P61" s="9" t="inlineStr"/>
+      <c r="Q61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
-      <c r="L62" s="7" t="n"/>
-      <c r="M62" s="7" t="n"/>
-      <c r="N62" s="7" t="n"/>
-      <c r="O62" s="7" t="n"/>
-      <c r="P62" s="7" t="n"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Оперативка</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>DDR5</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>64 ГБ</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 2x32GB 6000</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>DDR5 64GB 2x32 6000</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>DDR5</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>ноутбук, SO-DIMM, sodimm</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="inlineStr"/>
+      <c r="O62" s="9" t="inlineStr"/>
+      <c r="P62" s="9" t="inlineStr"/>
+      <c r="Q62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -3893,6 +4122,7 @@
       <c r="N63" s="7" t="n"/>
       <c r="O63" s="7" t="n"/>
       <c r="P63" s="7" t="n"/>
+      <c r="Q63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -3911,6 +4141,7 @@
       <c r="N64" s="7" t="n"/>
       <c r="O64" s="7" t="n"/>
       <c r="P64" s="7" t="n"/>
+      <c r="Q64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -3929,6 +4160,7 @@
       <c r="N65" s="7" t="n"/>
       <c r="O65" s="7" t="n"/>
       <c r="P65" s="7" t="n"/>
+      <c r="Q65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -3947,6 +4179,7 @@
       <c r="N66" s="7" t="n"/>
       <c r="O66" s="7" t="n"/>
       <c r="P66" s="7" t="n"/>
+      <c r="Q66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -3965,6 +4198,7 @@
       <c r="N67" s="7" t="n"/>
       <c r="O67" s="7" t="n"/>
       <c r="P67" s="7" t="n"/>
+      <c r="Q67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -3983,6 +4217,7 @@
       <c r="N68" s="7" t="n"/>
       <c r="O68" s="7" t="n"/>
       <c r="P68" s="7" t="n"/>
+      <c r="Q68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -4001,6 +4236,7 @@
       <c r="N69" s="7" t="n"/>
       <c r="O69" s="7" t="n"/>
       <c r="P69" s="7" t="n"/>
+      <c r="Q69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -4019,6 +4255,7 @@
       <c r="N70" s="7" t="n"/>
       <c r="O70" s="7" t="n"/>
       <c r="P70" s="7" t="n"/>
+      <c r="Q70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -4037,6 +4274,7 @@
       <c r="N71" s="7" t="n"/>
       <c r="O71" s="7" t="n"/>
       <c r="P71" s="7" t="n"/>
+      <c r="Q71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -4055,6 +4293,7 @@
       <c r="N72" s="7" t="n"/>
       <c r="O72" s="7" t="n"/>
       <c r="P72" s="7" t="n"/>
+      <c r="Q72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -4073,6 +4312,7 @@
       <c r="N73" s="7" t="n"/>
       <c r="O73" s="7" t="n"/>
       <c r="P73" s="7" t="n"/>
+      <c r="Q73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -4091,6 +4331,7 @@
       <c r="N74" s="7" t="n"/>
       <c r="O74" s="7" t="n"/>
       <c r="P74" s="7" t="n"/>
+      <c r="Q74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -4109,6 +4350,7 @@
       <c r="N75" s="7" t="n"/>
       <c r="O75" s="7" t="n"/>
       <c r="P75" s="7" t="n"/>
+      <c r="Q75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -4127,6 +4369,7 @@
       <c r="N76" s="7" t="n"/>
       <c r="O76" s="7" t="n"/>
       <c r="P76" s="7" t="n"/>
+      <c r="Q76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -4145,6 +4388,7 @@
       <c r="N77" s="7" t="n"/>
       <c r="O77" s="7" t="n"/>
       <c r="P77" s="7" t="n"/>
+      <c r="Q77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -4163,6 +4407,7 @@
       <c r="N78" s="7" t="n"/>
       <c r="O78" s="7" t="n"/>
       <c r="P78" s="7" t="n"/>
+      <c r="Q78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -4181,6 +4426,7 @@
       <c r="N79" s="7" t="n"/>
       <c r="O79" s="7" t="n"/>
       <c r="P79" s="7" t="n"/>
+      <c r="Q79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -4199,6 +4445,7 @@
       <c r="N80" s="7" t="n"/>
       <c r="O80" s="7" t="n"/>
       <c r="P80" s="7" t="n"/>
+      <c r="Q80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -4217,6 +4464,7 @@
       <c r="N81" s="7" t="n"/>
       <c r="O81" s="7" t="n"/>
       <c r="P81" s="7" t="n"/>
+      <c r="Q81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -4235,6 +4483,7 @@
       <c r="N82" s="7" t="n"/>
       <c r="O82" s="7" t="n"/>
       <c r="P82" s="7" t="n"/>
+      <c r="Q82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -4253,6 +4502,7 @@
       <c r="N83" s="7" t="n"/>
       <c r="O83" s="7" t="n"/>
       <c r="P83" s="7" t="n"/>
+      <c r="Q83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -4271,6 +4521,7 @@
       <c r="N84" s="7" t="n"/>
       <c r="O84" s="7" t="n"/>
       <c r="P84" s="7" t="n"/>
+      <c r="Q84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -4289,6 +4540,7 @@
       <c r="N85" s="7" t="n"/>
       <c r="O85" s="7" t="n"/>
       <c r="P85" s="7" t="n"/>
+      <c r="Q85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -4307,6 +4559,7 @@
       <c r="N86" s="7" t="n"/>
       <c r="O86" s="7" t="n"/>
       <c r="P86" s="7" t="n"/>
+      <c r="Q86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -4325,6 +4578,7 @@
       <c r="N87" s="7" t="n"/>
       <c r="O87" s="7" t="n"/>
       <c r="P87" s="7" t="n"/>
+      <c r="Q87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -4343,6 +4597,7 @@
       <c r="N88" s="7" t="n"/>
       <c r="O88" s="7" t="n"/>
       <c r="P88" s="7" t="n"/>
+      <c r="Q88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -4361,6 +4616,7 @@
       <c r="N89" s="7" t="n"/>
       <c r="O89" s="7" t="n"/>
       <c r="P89" s="7" t="n"/>
+      <c r="Q89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -4379,6 +4635,7 @@
       <c r="N90" s="7" t="n"/>
       <c r="O90" s="7" t="n"/>
       <c r="P90" s="7" t="n"/>
+      <c r="Q90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -4397,6 +4654,7 @@
       <c r="N91" s="7" t="n"/>
       <c r="O91" s="7" t="n"/>
       <c r="P91" s="7" t="n"/>
+      <c r="Q91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -4415,6 +4673,7 @@
       <c r="N92" s="7" t="n"/>
       <c r="O92" s="7" t="n"/>
       <c r="P92" s="7" t="n"/>
+      <c r="Q92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -4433,6 +4692,7 @@
       <c r="N93" s="7" t="n"/>
       <c r="O93" s="7" t="n"/>
       <c r="P93" s="7" t="n"/>
+      <c r="Q93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -4451,6 +4711,7 @@
       <c r="N94" s="7" t="n"/>
       <c r="O94" s="7" t="n"/>
       <c r="P94" s="7" t="n"/>
+      <c r="Q94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -4469,6 +4730,7 @@
       <c r="N95" s="7" t="n"/>
       <c r="O95" s="7" t="n"/>
       <c r="P95" s="7" t="n"/>
+      <c r="Q95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -4487,6 +4749,7 @@
       <c r="N96" s="7" t="n"/>
       <c r="O96" s="7" t="n"/>
       <c r="P96" s="7" t="n"/>
+      <c r="Q96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -4505,6 +4768,7 @@
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="7" t="n"/>
       <c r="P97" s="7" t="n"/>
+      <c r="Q97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -4523,6 +4787,7 @@
       <c r="N98" s="7" t="n"/>
       <c r="O98" s="7" t="n"/>
       <c r="P98" s="7" t="n"/>
+      <c r="Q98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -4541,6 +4806,7 @@
       <c r="N99" s="7" t="n"/>
       <c r="O99" s="7" t="n"/>
       <c r="P99" s="7" t="n"/>
+      <c r="Q99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -4559,6 +4825,7 @@
       <c r="N100" s="7" t="n"/>
       <c r="O100" s="7" t="n"/>
       <c r="P100" s="7" t="n"/>
+      <c r="Q100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -4577,6 +4844,7 @@
       <c r="N101" s="7" t="n"/>
       <c r="O101" s="7" t="n"/>
       <c r="P101" s="7" t="n"/>
+      <c r="Q101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -4595,6 +4863,7 @@
       <c r="N102" s="7" t="n"/>
       <c r="O102" s="7" t="n"/>
       <c r="P102" s="7" t="n"/>
+      <c r="Q102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -4613,6 +4882,7 @@
       <c r="N103" s="7" t="n"/>
       <c r="O103" s="7" t="n"/>
       <c r="P103" s="7" t="n"/>
+      <c r="Q103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -4631,6 +4901,7 @@
       <c r="N104" s="7" t="n"/>
       <c r="O104" s="7" t="n"/>
       <c r="P104" s="7" t="n"/>
+      <c r="Q104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -4649,6 +4920,7 @@
       <c r="N105" s="7" t="n"/>
       <c r="O105" s="7" t="n"/>
       <c r="P105" s="7" t="n"/>
+      <c r="Q105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -4667,6 +4939,7 @@
       <c r="N106" s="7" t="n"/>
       <c r="O106" s="7" t="n"/>
       <c r="P106" s="7" t="n"/>
+      <c r="Q106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -4685,6 +4958,7 @@
       <c r="N107" s="7" t="n"/>
       <c r="O107" s="7" t="n"/>
       <c r="P107" s="7" t="n"/>
+      <c r="Q107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -4703,6 +4977,7 @@
       <c r="N108" s="7" t="n"/>
       <c r="O108" s="7" t="n"/>
       <c r="P108" s="7" t="n"/>
+      <c r="Q108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -4721,6 +4996,7 @@
       <c r="N109" s="7" t="n"/>
       <c r="O109" s="7" t="n"/>
       <c r="P109" s="7" t="n"/>
+      <c r="Q109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -4739,6 +5015,7 @@
       <c r="N110" s="7" t="n"/>
       <c r="O110" s="7" t="n"/>
       <c r="P110" s="7" t="n"/>
+      <c r="Q110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -4757,6 +5034,7 @@
       <c r="N111" s="7" t="n"/>
       <c r="O111" s="7" t="n"/>
       <c r="P111" s="7" t="n"/>
+      <c r="Q111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -4775,6 +5053,7 @@
       <c r="N112" s="7" t="n"/>
       <c r="O112" s="7" t="n"/>
       <c r="P112" s="7" t="n"/>
+      <c r="Q112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -4793,6 +5072,7 @@
       <c r="N113" s="7" t="n"/>
       <c r="O113" s="7" t="n"/>
       <c r="P113" s="7" t="n"/>
+      <c r="Q113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -4811,6 +5091,7 @@
       <c r="N114" s="7" t="n"/>
       <c r="O114" s="7" t="n"/>
       <c r="P114" s="7" t="n"/>
+      <c r="Q114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -4829,6 +5110,7 @@
       <c r="N115" s="7" t="n"/>
       <c r="O115" s="7" t="n"/>
       <c r="P115" s="7" t="n"/>
+      <c r="Q115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -4847,6 +5129,7 @@
       <c r="N116" s="7" t="n"/>
       <c r="O116" s="7" t="n"/>
       <c r="P116" s="7" t="n"/>
+      <c r="Q116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -4865,6 +5148,7 @@
       <c r="N117" s="7" t="n"/>
       <c r="O117" s="7" t="n"/>
       <c r="P117" s="7" t="n"/>
+      <c r="Q117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -4883,6 +5167,7 @@
       <c r="N118" s="7" t="n"/>
       <c r="O118" s="7" t="n"/>
       <c r="P118" s="7" t="n"/>
+      <c r="Q118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -4901,6 +5186,7 @@
       <c r="N119" s="7" t="n"/>
       <c r="O119" s="7" t="n"/>
       <c r="P119" s="7" t="n"/>
+      <c r="Q119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -4919,6 +5205,7 @@
       <c r="N120" s="7" t="n"/>
       <c r="O120" s="7" t="n"/>
       <c r="P120" s="7" t="n"/>
+      <c r="Q120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -4937,6 +5224,7 @@
       <c r="N121" s="7" t="n"/>
       <c r="O121" s="7" t="n"/>
       <c r="P121" s="7" t="n"/>
+      <c r="Q121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -4955,6 +5243,7 @@
       <c r="N122" s="7" t="n"/>
       <c r="O122" s="7" t="n"/>
       <c r="P122" s="7" t="n"/>
+      <c r="Q122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -4973,6 +5262,7 @@
       <c r="N123" s="7" t="n"/>
       <c r="O123" s="7" t="n"/>
       <c r="P123" s="7" t="n"/>
+      <c r="Q123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -4991,6 +5281,7 @@
       <c r="N124" s="7" t="n"/>
       <c r="O124" s="7" t="n"/>
       <c r="P124" s="7" t="n"/>
+      <c r="Q124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -5009,6 +5300,7 @@
       <c r="N125" s="7" t="n"/>
       <c r="O125" s="7" t="n"/>
       <c r="P125" s="7" t="n"/>
+      <c r="Q125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -5027,6 +5319,7 @@
       <c r="N126" s="7" t="n"/>
       <c r="O126" s="7" t="n"/>
       <c r="P126" s="7" t="n"/>
+      <c r="Q126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -5045,6 +5338,7 @@
       <c r="N127" s="7" t="n"/>
       <c r="O127" s="7" t="n"/>
       <c r="P127" s="7" t="n"/>
+      <c r="Q127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -5063,6 +5357,7 @@
       <c r="N128" s="7" t="n"/>
       <c r="O128" s="7" t="n"/>
       <c r="P128" s="7" t="n"/>
+      <c r="Q128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -5081,6 +5376,7 @@
       <c r="N129" s="7" t="n"/>
       <c r="O129" s="7" t="n"/>
       <c r="P129" s="7" t="n"/>
+      <c r="Q129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -5099,6 +5395,7 @@
       <c r="N130" s="7" t="n"/>
       <c r="O130" s="7" t="n"/>
       <c r="P130" s="7" t="n"/>
+      <c r="Q130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -5117,6 +5414,7 @@
       <c r="N131" s="7" t="n"/>
       <c r="O131" s="7" t="n"/>
       <c r="P131" s="7" t="n"/>
+      <c r="Q131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -5135,6 +5433,7 @@
       <c r="N132" s="7" t="n"/>
       <c r="O132" s="7" t="n"/>
       <c r="P132" s="7" t="n"/>
+      <c r="Q132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -5153,6 +5452,7 @@
       <c r="N133" s="7" t="n"/>
       <c r="O133" s="7" t="n"/>
       <c r="P133" s="7" t="n"/>
+      <c r="Q133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -5171,6 +5471,7 @@
       <c r="N134" s="7" t="n"/>
       <c r="O134" s="7" t="n"/>
       <c r="P134" s="7" t="n"/>
+      <c r="Q134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -5189,6 +5490,7 @@
       <c r="N135" s="7" t="n"/>
       <c r="O135" s="7" t="n"/>
       <c r="P135" s="7" t="n"/>
+      <c r="Q135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -5207,6 +5509,7 @@
       <c r="N136" s="7" t="n"/>
       <c r="O136" s="7" t="n"/>
       <c r="P136" s="7" t="n"/>
+      <c r="Q136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -5225,6 +5528,7 @@
       <c r="N137" s="7" t="n"/>
       <c r="O137" s="7" t="n"/>
       <c r="P137" s="7" t="n"/>
+      <c r="Q137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -5243,6 +5547,7 @@
       <c r="N138" s="7" t="n"/>
       <c r="O138" s="7" t="n"/>
       <c r="P138" s="7" t="n"/>
+      <c r="Q138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -5261,6 +5566,7 @@
       <c r="N139" s="7" t="n"/>
       <c r="O139" s="7" t="n"/>
       <c r="P139" s="7" t="n"/>
+      <c r="Q139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -5279,6 +5585,7 @@
       <c r="N140" s="7" t="n"/>
       <c r="O140" s="7" t="n"/>
       <c r="P140" s="7" t="n"/>
+      <c r="Q140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -5297,6 +5604,7 @@
       <c r="N141" s="7" t="n"/>
       <c r="O141" s="7" t="n"/>
       <c r="P141" s="7" t="n"/>
+      <c r="Q141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -5315,6 +5623,7 @@
       <c r="N142" s="7" t="n"/>
       <c r="O142" s="7" t="n"/>
       <c r="P142" s="7" t="n"/>
+      <c r="Q142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -5333,6 +5642,7 @@
       <c r="N143" s="7" t="n"/>
       <c r="O143" s="7" t="n"/>
       <c r="P143" s="7" t="n"/>
+      <c r="Q143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -5351,6 +5661,7 @@
       <c r="N144" s="7" t="n"/>
       <c r="O144" s="7" t="n"/>
       <c r="P144" s="7" t="n"/>
+      <c r="Q144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -5369,6 +5680,7 @@
       <c r="N145" s="7" t="n"/>
       <c r="O145" s="7" t="n"/>
       <c r="P145" s="7" t="n"/>
+      <c r="Q145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -5387,6 +5699,7 @@
       <c r="N146" s="7" t="n"/>
       <c r="O146" s="7" t="n"/>
       <c r="P146" s="7" t="n"/>
+      <c r="Q146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -5405,6 +5718,7 @@
       <c r="N147" s="7" t="n"/>
       <c r="O147" s="7" t="n"/>
       <c r="P147" s="7" t="n"/>
+      <c r="Q147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -5423,6 +5737,7 @@
       <c r="N148" s="7" t="n"/>
       <c r="O148" s="7" t="n"/>
       <c r="P148" s="7" t="n"/>
+      <c r="Q148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -5441,6 +5756,7 @@
       <c r="N149" s="7" t="n"/>
       <c r="O149" s="7" t="n"/>
       <c r="P149" s="7" t="n"/>
+      <c r="Q149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -5459,6 +5775,7 @@
       <c r="N150" s="7" t="n"/>
       <c r="O150" s="7" t="n"/>
       <c r="P150" s="7" t="n"/>
+      <c r="Q150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -5477,6 +5794,7 @@
       <c r="N151" s="7" t="n"/>
       <c r="O151" s="7" t="n"/>
       <c r="P151" s="7" t="n"/>
+      <c r="Q151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -5495,6 +5813,7 @@
       <c r="N152" s="7" t="n"/>
       <c r="O152" s="7" t="n"/>
       <c r="P152" s="7" t="n"/>
+      <c r="Q152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -5513,6 +5832,7 @@
       <c r="N153" s="7" t="n"/>
       <c r="O153" s="7" t="n"/>
       <c r="P153" s="7" t="n"/>
+      <c r="Q153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -5531,6 +5851,7 @@
       <c r="N154" s="7" t="n"/>
       <c r="O154" s="7" t="n"/>
       <c r="P154" s="7" t="n"/>
+      <c r="Q154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -5549,6 +5870,7 @@
       <c r="N155" s="7" t="n"/>
       <c r="O155" s="7" t="n"/>
       <c r="P155" s="7" t="n"/>
+      <c r="Q155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -5567,6 +5889,7 @@
       <c r="N156" s="7" t="n"/>
       <c r="O156" s="7" t="n"/>
       <c r="P156" s="7" t="n"/>
+      <c r="Q156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -5585,6 +5908,7 @@
       <c r="N157" s="7" t="n"/>
       <c r="O157" s="7" t="n"/>
       <c r="P157" s="7" t="n"/>
+      <c r="Q157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -5603,6 +5927,7 @@
       <c r="N158" s="7" t="n"/>
       <c r="O158" s="7" t="n"/>
       <c r="P158" s="7" t="n"/>
+      <c r="Q158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -5621,6 +5946,7 @@
       <c r="N159" s="7" t="n"/>
       <c r="O159" s="7" t="n"/>
       <c r="P159" s="7" t="n"/>
+      <c r="Q159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -5639,6 +5965,7 @@
       <c r="N160" s="7" t="n"/>
       <c r="O160" s="7" t="n"/>
       <c r="P160" s="7" t="n"/>
+      <c r="Q160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -5657,6 +5984,7 @@
       <c r="N161" s="7" t="n"/>
       <c r="O161" s="7" t="n"/>
       <c r="P161" s="7" t="n"/>
+      <c r="Q161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -5675,6 +6003,7 @@
       <c r="N162" s="7" t="n"/>
       <c r="O162" s="7" t="n"/>
       <c r="P162" s="7" t="n"/>
+      <c r="Q162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -5693,6 +6022,7 @@
       <c r="N163" s="7" t="n"/>
       <c r="O163" s="7" t="n"/>
       <c r="P163" s="7" t="n"/>
+      <c r="Q163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -5711,6 +6041,7 @@
       <c r="N164" s="7" t="n"/>
       <c r="O164" s="7" t="n"/>
       <c r="P164" s="7" t="n"/>
+      <c r="Q164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -5729,6 +6060,7 @@
       <c r="N165" s="7" t="n"/>
       <c r="O165" s="7" t="n"/>
       <c r="P165" s="7" t="n"/>
+      <c r="Q165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -5747,6 +6079,7 @@
       <c r="N166" s="7" t="n"/>
       <c r="O166" s="7" t="n"/>
       <c r="P166" s="7" t="n"/>
+      <c r="Q166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -5765,6 +6098,7 @@
       <c r="N167" s="7" t="n"/>
       <c r="O167" s="7" t="n"/>
       <c r="P167" s="7" t="n"/>
+      <c r="Q167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -5783,6 +6117,7 @@
       <c r="N168" s="7" t="n"/>
       <c r="O168" s="7" t="n"/>
       <c r="P168" s="7" t="n"/>
+      <c r="Q168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -5801,6 +6136,7 @@
       <c r="N169" s="7" t="n"/>
       <c r="O169" s="7" t="n"/>
       <c r="P169" s="7" t="n"/>
+      <c r="Q169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -5819,6 +6155,7 @@
       <c r="N170" s="7" t="n"/>
       <c r="O170" s="7" t="n"/>
       <c r="P170" s="7" t="n"/>
+      <c r="Q170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -5837,6 +6174,7 @@
       <c r="N171" s="7" t="n"/>
       <c r="O171" s="7" t="n"/>
       <c r="P171" s="7" t="n"/>
+      <c r="Q171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -5855,6 +6193,7 @@
       <c r="N172" s="7" t="n"/>
       <c r="O172" s="7" t="n"/>
       <c r="P172" s="7" t="n"/>
+      <c r="Q172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -5873,6 +6212,7 @@
       <c r="N173" s="7" t="n"/>
       <c r="O173" s="7" t="n"/>
       <c r="P173" s="7" t="n"/>
+      <c r="Q173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -5891,6 +6231,7 @@
       <c r="N174" s="7" t="n"/>
       <c r="O174" s="7" t="n"/>
       <c r="P174" s="7" t="n"/>
+      <c r="Q174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -5909,6 +6250,7 @@
       <c r="N175" s="7" t="n"/>
       <c r="O175" s="7" t="n"/>
       <c r="P175" s="7" t="n"/>
+      <c r="Q175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -5927,6 +6269,7 @@
       <c r="N176" s="7" t="n"/>
       <c r="O176" s="7" t="n"/>
       <c r="P176" s="7" t="n"/>
+      <c r="Q176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -5945,6 +6288,7 @@
       <c r="N177" s="7" t="n"/>
       <c r="O177" s="7" t="n"/>
       <c r="P177" s="7" t="n"/>
+      <c r="Q177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -5963,6 +6307,7 @@
       <c r="N178" s="7" t="n"/>
       <c r="O178" s="7" t="n"/>
       <c r="P178" s="7" t="n"/>
+      <c r="Q178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -5981,6 +6326,7 @@
       <c r="N179" s="7" t="n"/>
       <c r="O179" s="7" t="n"/>
       <c r="P179" s="7" t="n"/>
+      <c r="Q179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -5999,6 +6345,7 @@
       <c r="N180" s="7" t="n"/>
       <c r="O180" s="7" t="n"/>
       <c r="P180" s="7" t="n"/>
+      <c r="Q180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -6017,6 +6364,7 @@
       <c r="N181" s="7" t="n"/>
       <c r="O181" s="7" t="n"/>
       <c r="P181" s="7" t="n"/>
+      <c r="Q181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -6035,6 +6383,7 @@
       <c r="N182" s="7" t="n"/>
       <c r="O182" s="7" t="n"/>
       <c r="P182" s="7" t="n"/>
+      <c r="Q182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -6053,6 +6402,7 @@
       <c r="N183" s="7" t="n"/>
       <c r="O183" s="7" t="n"/>
       <c r="P183" s="7" t="n"/>
+      <c r="Q183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -6071,6 +6421,7 @@
       <c r="N184" s="7" t="n"/>
       <c r="O184" s="7" t="n"/>
       <c r="P184" s="7" t="n"/>
+      <c r="Q184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -6089,6 +6440,7 @@
       <c r="N185" s="7" t="n"/>
       <c r="O185" s="7" t="n"/>
       <c r="P185" s="7" t="n"/>
+      <c r="Q185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -6107,6 +6459,7 @@
       <c r="N186" s="7" t="n"/>
       <c r="O186" s="7" t="n"/>
       <c r="P186" s="7" t="n"/>
+      <c r="Q186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -6125,6 +6478,7 @@
       <c r="N187" s="7" t="n"/>
       <c r="O187" s="7" t="n"/>
       <c r="P187" s="7" t="n"/>
+      <c r="Q187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -6143,6 +6497,7 @@
       <c r="N188" s="7" t="n"/>
       <c r="O188" s="7" t="n"/>
       <c r="P188" s="7" t="n"/>
+      <c r="Q188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -6161,6 +6516,7 @@
       <c r="N189" s="7" t="n"/>
       <c r="O189" s="7" t="n"/>
       <c r="P189" s="7" t="n"/>
+      <c r="Q189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -6179,6 +6535,7 @@
       <c r="N190" s="7" t="n"/>
       <c r="O190" s="7" t="n"/>
       <c r="P190" s="7" t="n"/>
+      <c r="Q190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -6197,6 +6554,7 @@
       <c r="N191" s="7" t="n"/>
       <c r="O191" s="7" t="n"/>
       <c r="P191" s="7" t="n"/>
+      <c r="Q191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -6215,6 +6573,7 @@
       <c r="N192" s="7" t="n"/>
       <c r="O192" s="7" t="n"/>
       <c r="P192" s="7" t="n"/>
+      <c r="Q192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -6233,6 +6592,7 @@
       <c r="N193" s="7" t="n"/>
       <c r="O193" s="7" t="n"/>
       <c r="P193" s="7" t="n"/>
+      <c r="Q193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -6251,6 +6611,7 @@
       <c r="N194" s="7" t="n"/>
       <c r="O194" s="7" t="n"/>
       <c r="P194" s="7" t="n"/>
+      <c r="Q194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -6269,6 +6630,7 @@
       <c r="N195" s="7" t="n"/>
       <c r="O195" s="7" t="n"/>
       <c r="P195" s="7" t="n"/>
+      <c r="Q195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -6287,6 +6649,7 @@
       <c r="N196" s="7" t="n"/>
       <c r="O196" s="7" t="n"/>
       <c r="P196" s="7" t="n"/>
+      <c r="Q196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -6305,6 +6668,7 @@
       <c r="N197" s="7" t="n"/>
       <c r="O197" s="7" t="n"/>
       <c r="P197" s="7" t="n"/>
+      <c r="Q197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -6323,6 +6687,7 @@
       <c r="N198" s="7" t="n"/>
       <c r="O198" s="7" t="n"/>
       <c r="P198" s="7" t="n"/>
+      <c r="Q198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -6341,6 +6706,7 @@
       <c r="N199" s="7" t="n"/>
       <c r="O199" s="7" t="n"/>
       <c r="P199" s="7" t="n"/>
+      <c r="Q199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -6359,6 +6725,7 @@
       <c r="N200" s="7" t="n"/>
       <c r="O200" s="7" t="n"/>
       <c r="P200" s="7" t="n"/>
+      <c r="Q200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -6377,6 +6744,7 @@
       <c r="N201" s="7" t="n"/>
       <c r="O201" s="7" t="n"/>
       <c r="P201" s="7" t="n"/>
+      <c r="Q201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -6395,6 +6763,7 @@
       <c r="N202" s="7" t="n"/>
       <c r="O202" s="7" t="n"/>
       <c r="P202" s="7" t="n"/>
+      <c r="Q202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -6413,6 +6782,7 @@
       <c r="N203" s="7" t="n"/>
       <c r="O203" s="7" t="n"/>
       <c r="P203" s="7" t="n"/>
+      <c r="Q203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -6431,6 +6801,7 @@
       <c r="N204" s="7" t="n"/>
       <c r="O204" s="7" t="n"/>
       <c r="P204" s="7" t="n"/>
+      <c r="Q204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -6449,6 +6820,7 @@
       <c r="N205" s="7" t="n"/>
       <c r="O205" s="7" t="n"/>
       <c r="P205" s="7" t="n"/>
+      <c r="Q205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -6467,6 +6839,7 @@
       <c r="N206" s="7" t="n"/>
       <c r="O206" s="7" t="n"/>
       <c r="P206" s="7" t="n"/>
+      <c r="Q206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -6485,6 +6858,7 @@
       <c r="N207" s="7" t="n"/>
       <c r="O207" s="7" t="n"/>
       <c r="P207" s="7" t="n"/>
+      <c r="Q207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -6503,6 +6877,7 @@
       <c r="N208" s="7" t="n"/>
       <c r="O208" s="7" t="n"/>
       <c r="P208" s="7" t="n"/>
+      <c r="Q208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -6521,6 +6896,7 @@
       <c r="N209" s="7" t="n"/>
       <c r="O209" s="7" t="n"/>
       <c r="P209" s="7" t="n"/>
+      <c r="Q209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -6539,6 +6915,7 @@
       <c r="N210" s="7" t="n"/>
       <c r="O210" s="7" t="n"/>
       <c r="P210" s="7" t="n"/>
+      <c r="Q210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -6557,6 +6934,7 @@
       <c r="N211" s="7" t="n"/>
       <c r="O211" s="7" t="n"/>
       <c r="P211" s="7" t="n"/>
+      <c r="Q211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -6575,6 +6953,7 @@
       <c r="N212" s="7" t="n"/>
       <c r="O212" s="7" t="n"/>
       <c r="P212" s="7" t="n"/>
+      <c r="Q212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -6593,6 +6972,7 @@
       <c r="N213" s="7" t="n"/>
       <c r="O213" s="7" t="n"/>
       <c r="P213" s="7" t="n"/>
+      <c r="Q213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -6611,6 +6991,7 @@
       <c r="N214" s="7" t="n"/>
       <c r="O214" s="7" t="n"/>
       <c r="P214" s="7" t="n"/>
+      <c r="Q214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -6629,6 +7010,7 @@
       <c r="N215" s="7" t="n"/>
       <c r="O215" s="7" t="n"/>
       <c r="P215" s="7" t="n"/>
+      <c r="Q215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -6647,6 +7029,7 @@
       <c r="N216" s="7" t="n"/>
       <c r="O216" s="7" t="n"/>
       <c r="P216" s="7" t="n"/>
+      <c r="Q216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -6665,6 +7048,7 @@
       <c r="N217" s="7" t="n"/>
       <c r="O217" s="7" t="n"/>
       <c r="P217" s="7" t="n"/>
+      <c r="Q217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -6683,6 +7067,7 @@
       <c r="N218" s="7" t="n"/>
       <c r="O218" s="7" t="n"/>
       <c r="P218" s="7" t="n"/>
+      <c r="Q218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -6701,6 +7086,7 @@
       <c r="N219" s="7" t="n"/>
       <c r="O219" s="7" t="n"/>
       <c r="P219" s="7" t="n"/>
+      <c r="Q219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -6719,6 +7105,7 @@
       <c r="N220" s="7" t="n"/>
       <c r="O220" s="7" t="n"/>
       <c r="P220" s="7" t="n"/>
+      <c r="Q220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -6737,6 +7124,7 @@
       <c r="N221" s="7" t="n"/>
       <c r="O221" s="7" t="n"/>
       <c r="P221" s="7" t="n"/>
+      <c r="Q221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -6755,6 +7143,7 @@
       <c r="N222" s="7" t="n"/>
       <c r="O222" s="7" t="n"/>
       <c r="P222" s="7" t="n"/>
+      <c r="Q222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -6773,6 +7162,7 @@
       <c r="N223" s="7" t="n"/>
       <c r="O223" s="7" t="n"/>
       <c r="P223" s="7" t="n"/>
+      <c r="Q223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -6791,6 +7181,7 @@
       <c r="N224" s="7" t="n"/>
       <c r="O224" s="7" t="n"/>
       <c r="P224" s="7" t="n"/>
+      <c r="Q224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -6809,6 +7200,7 @@
       <c r="N225" s="7" t="n"/>
       <c r="O225" s="7" t="n"/>
       <c r="P225" s="7" t="n"/>
+      <c r="Q225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -6827,6 +7219,7 @@
       <c r="N226" s="7" t="n"/>
       <c r="O226" s="7" t="n"/>
       <c r="P226" s="7" t="n"/>
+      <c r="Q226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -6845,6 +7238,7 @@
       <c r="N227" s="7" t="n"/>
       <c r="O227" s="7" t="n"/>
       <c r="P227" s="7" t="n"/>
+      <c r="Q227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -6863,6 +7257,7 @@
       <c r="N228" s="7" t="n"/>
       <c r="O228" s="7" t="n"/>
       <c r="P228" s="7" t="n"/>
+      <c r="Q228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -6881,6 +7276,7 @@
       <c r="N229" s="7" t="n"/>
       <c r="O229" s="7" t="n"/>
       <c r="P229" s="7" t="n"/>
+      <c r="Q229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -6899,6 +7295,7 @@
       <c r="N230" s="7" t="n"/>
       <c r="O230" s="7" t="n"/>
       <c r="P230" s="7" t="n"/>
+      <c r="Q230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -6917,6 +7314,7 @@
       <c r="N231" s="7" t="n"/>
       <c r="O231" s="7" t="n"/>
       <c r="P231" s="7" t="n"/>
+      <c r="Q231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -6935,6 +7333,7 @@
       <c r="N232" s="7" t="n"/>
       <c r="O232" s="7" t="n"/>
       <c r="P232" s="7" t="n"/>
+      <c r="Q232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -6953,6 +7352,7 @@
       <c r="N233" s="7" t="n"/>
       <c r="O233" s="7" t="n"/>
       <c r="P233" s="7" t="n"/>
+      <c r="Q233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -6971,6 +7371,7 @@
       <c r="N234" s="7" t="n"/>
       <c r="O234" s="7" t="n"/>
       <c r="P234" s="7" t="n"/>
+      <c r="Q234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -6989,6 +7390,7 @@
       <c r="N235" s="7" t="n"/>
       <c r="O235" s="7" t="n"/>
       <c r="P235" s="7" t="n"/>
+      <c r="Q235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -7007,6 +7409,7 @@
       <c r="N236" s="7" t="n"/>
       <c r="O236" s="7" t="n"/>
       <c r="P236" s="7" t="n"/>
+      <c r="Q236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -7025,6 +7428,7 @@
       <c r="N237" s="7" t="n"/>
       <c r="O237" s="7" t="n"/>
       <c r="P237" s="7" t="n"/>
+      <c r="Q237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -7043,6 +7447,7 @@
       <c r="N238" s="7" t="n"/>
       <c r="O238" s="7" t="n"/>
       <c r="P238" s="7" t="n"/>
+      <c r="Q238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -7061,6 +7466,7 @@
       <c r="N239" s="7" t="n"/>
       <c r="O239" s="7" t="n"/>
       <c r="P239" s="7" t="n"/>
+      <c r="Q239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -7079,6 +7485,7 @@
       <c r="N240" s="7" t="n"/>
       <c r="O240" s="7" t="n"/>
       <c r="P240" s="7" t="n"/>
+      <c r="Q240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -7097,6 +7504,7 @@
       <c r="N241" s="7" t="n"/>
       <c r="O241" s="7" t="n"/>
       <c r="P241" s="7" t="n"/>
+      <c r="Q241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -7115,6 +7523,7 @@
       <c r="N242" s="7" t="n"/>
       <c r="O242" s="7" t="n"/>
       <c r="P242" s="7" t="n"/>
+      <c r="Q242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -7133,6 +7542,7 @@
       <c r="N243" s="7" t="n"/>
       <c r="O243" s="7" t="n"/>
       <c r="P243" s="7" t="n"/>
+      <c r="Q243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -7151,6 +7561,7 @@
       <c r="N244" s="7" t="n"/>
       <c r="O244" s="7" t="n"/>
       <c r="P244" s="7" t="n"/>
+      <c r="Q244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -7169,6 +7580,7 @@
       <c r="N245" s="7" t="n"/>
       <c r="O245" s="7" t="n"/>
       <c r="P245" s="7" t="n"/>
+      <c r="Q245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -7187,6 +7599,7 @@
       <c r="N246" s="7" t="n"/>
       <c r="O246" s="7" t="n"/>
       <c r="P246" s="7" t="n"/>
+      <c r="Q246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -7205,6 +7618,7 @@
       <c r="N247" s="7" t="n"/>
       <c r="O247" s="7" t="n"/>
       <c r="P247" s="7" t="n"/>
+      <c r="Q247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -7223,6 +7637,7 @@
       <c r="N248" s="7" t="n"/>
       <c r="O248" s="7" t="n"/>
       <c r="P248" s="7" t="n"/>
+      <c r="Q248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -7241,6 +7656,7 @@
       <c r="N249" s="7" t="n"/>
       <c r="O249" s="7" t="n"/>
       <c r="P249" s="7" t="n"/>
+      <c r="Q249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -7259,6 +7675,7 @@
       <c r="N250" s="7" t="n"/>
       <c r="O250" s="7" t="n"/>
       <c r="P250" s="7" t="n"/>
+      <c r="Q250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -7277,6 +7694,7 @@
       <c r="N251" s="7" t="n"/>
       <c r="O251" s="7" t="n"/>
       <c r="P251" s="7" t="n"/>
+      <c r="Q251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -7295,6 +7713,7 @@
       <c r="N252" s="7" t="n"/>
       <c r="O252" s="7" t="n"/>
       <c r="P252" s="7" t="n"/>
+      <c r="Q252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -7313,6 +7732,7 @@
       <c r="N253" s="7" t="n"/>
       <c r="O253" s="7" t="n"/>
       <c r="P253" s="7" t="n"/>
+      <c r="Q253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -7331,6 +7751,7 @@
       <c r="N254" s="7" t="n"/>
       <c r="O254" s="7" t="n"/>
       <c r="P254" s="7" t="n"/>
+      <c r="Q254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -7349,6 +7770,7 @@
       <c r="N255" s="7" t="n"/>
       <c r="O255" s="7" t="n"/>
       <c r="P255" s="7" t="n"/>
+      <c r="Q255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -7367,6 +7789,7 @@
       <c r="N256" s="7" t="n"/>
       <c r="O256" s="7" t="n"/>
       <c r="P256" s="7" t="n"/>
+      <c r="Q256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -7385,6 +7808,7 @@
       <c r="N257" s="7" t="n"/>
       <c r="O257" s="7" t="n"/>
       <c r="P257" s="7" t="n"/>
+      <c r="Q257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -7403,6 +7827,7 @@
       <c r="N258" s="7" t="n"/>
       <c r="O258" s="7" t="n"/>
       <c r="P258" s="7" t="n"/>
+      <c r="Q258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -7421,6 +7846,7 @@
       <c r="N259" s="7" t="n"/>
       <c r="O259" s="7" t="n"/>
       <c r="P259" s="7" t="n"/>
+      <c r="Q259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -7439,6 +7865,7 @@
       <c r="N260" s="7" t="n"/>
       <c r="O260" s="7" t="n"/>
       <c r="P260" s="7" t="n"/>
+      <c r="Q260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -7457,6 +7884,7 @@
       <c r="N261" s="7" t="n"/>
       <c r="O261" s="7" t="n"/>
       <c r="P261" s="7" t="n"/>
+      <c r="Q261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -7475,6 +7903,7 @@
       <c r="N262" s="7" t="n"/>
       <c r="O262" s="7" t="n"/>
       <c r="P262" s="7" t="n"/>
+      <c r="Q262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -7493,6 +7922,7 @@
       <c r="N263" s="7" t="n"/>
       <c r="O263" s="7" t="n"/>
       <c r="P263" s="7" t="n"/>
+      <c r="Q263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -7511,6 +7941,7 @@
       <c r="N264" s="7" t="n"/>
       <c r="O264" s="7" t="n"/>
       <c r="P264" s="7" t="n"/>
+      <c r="Q264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -7529,6 +7960,7 @@
       <c r="N265" s="7" t="n"/>
       <c r="O265" s="7" t="n"/>
       <c r="P265" s="7" t="n"/>
+      <c r="Q265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -7547,6 +7979,7 @@
       <c r="N266" s="7" t="n"/>
       <c r="O266" s="7" t="n"/>
       <c r="P266" s="7" t="n"/>
+      <c r="Q266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -7565,6 +7998,7 @@
       <c r="N267" s="7" t="n"/>
       <c r="O267" s="7" t="n"/>
       <c r="P267" s="7" t="n"/>
+      <c r="Q267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -7583,6 +8017,7 @@
       <c r="N268" s="7" t="n"/>
       <c r="O268" s="7" t="n"/>
       <c r="P268" s="7" t="n"/>
+      <c r="Q268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -7601,6 +8036,7 @@
       <c r="N269" s="7" t="n"/>
       <c r="O269" s="7" t="n"/>
       <c r="P269" s="7" t="n"/>
+      <c r="Q269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -7619,6 +8055,7 @@
       <c r="N270" s="7" t="n"/>
       <c r="O270" s="7" t="n"/>
       <c r="P270" s="7" t="n"/>
+      <c r="Q270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -7637,6 +8074,7 @@
       <c r="N271" s="7" t="n"/>
       <c r="O271" s="7" t="n"/>
       <c r="P271" s="7" t="n"/>
+      <c r="Q271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -7655,6 +8093,7 @@
       <c r="N272" s="7" t="n"/>
       <c r="O272" s="7" t="n"/>
       <c r="P272" s="7" t="n"/>
+      <c r="Q272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -7673,6 +8112,7 @@
       <c r="N273" s="7" t="n"/>
       <c r="O273" s="7" t="n"/>
       <c r="P273" s="7" t="n"/>
+      <c r="Q273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -7691,6 +8131,7 @@
       <c r="N274" s="7" t="n"/>
       <c r="O274" s="7" t="n"/>
       <c r="P274" s="7" t="n"/>
+      <c r="Q274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -7709,6 +8150,7 @@
       <c r="N275" s="7" t="n"/>
       <c r="O275" s="7" t="n"/>
       <c r="P275" s="7" t="n"/>
+      <c r="Q275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -7727,6 +8169,7 @@
       <c r="N276" s="7" t="n"/>
       <c r="O276" s="7" t="n"/>
       <c r="P276" s="7" t="n"/>
+      <c r="Q276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -7745,6 +8188,7 @@
       <c r="N277" s="7" t="n"/>
       <c r="O277" s="7" t="n"/>
       <c r="P277" s="7" t="n"/>
+      <c r="Q277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -7763,6 +8207,7 @@
       <c r="N278" s="7" t="n"/>
       <c r="O278" s="7" t="n"/>
       <c r="P278" s="7" t="n"/>
+      <c r="Q278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -7781,6 +8226,7 @@
       <c r="N279" s="7" t="n"/>
       <c r="O279" s="7" t="n"/>
       <c r="P279" s="7" t="n"/>
+      <c r="Q279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -7799,6 +8245,7 @@
       <c r="N280" s="7" t="n"/>
       <c r="O280" s="7" t="n"/>
       <c r="P280" s="7" t="n"/>
+      <c r="Q280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -7817,6 +8264,7 @@
       <c r="N281" s="7" t="n"/>
       <c r="O281" s="7" t="n"/>
       <c r="P281" s="7" t="n"/>
+      <c r="Q281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -7835,6 +8283,7 @@
       <c r="N282" s="7" t="n"/>
       <c r="O282" s="7" t="n"/>
       <c r="P282" s="7" t="n"/>
+      <c r="Q282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -7853,6 +8302,7 @@
       <c r="N283" s="7" t="n"/>
       <c r="O283" s="7" t="n"/>
       <c r="P283" s="7" t="n"/>
+      <c r="Q283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -7871,6 +8321,7 @@
       <c r="N284" s="7" t="n"/>
       <c r="O284" s="7" t="n"/>
       <c r="P284" s="7" t="n"/>
+      <c r="Q284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -7889,6 +8340,7 @@
       <c r="N285" s="7" t="n"/>
       <c r="O285" s="7" t="n"/>
       <c r="P285" s="7" t="n"/>
+      <c r="Q285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -7907,6 +8359,7 @@
       <c r="N286" s="7" t="n"/>
       <c r="O286" s="7" t="n"/>
       <c r="P286" s="7" t="n"/>
+      <c r="Q286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -7925,6 +8378,7 @@
       <c r="N287" s="7" t="n"/>
       <c r="O287" s="7" t="n"/>
       <c r="P287" s="7" t="n"/>
+      <c r="Q287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -7943,6 +8397,7 @@
       <c r="N288" s="7" t="n"/>
       <c r="O288" s="7" t="n"/>
       <c r="P288" s="7" t="n"/>
+      <c r="Q288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -7961,6 +8416,7 @@
       <c r="N289" s="7" t="n"/>
       <c r="O289" s="7" t="n"/>
       <c r="P289" s="7" t="n"/>
+      <c r="Q289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -7979,6 +8435,7 @@
       <c r="N290" s="7" t="n"/>
       <c r="O290" s="7" t="n"/>
       <c r="P290" s="7" t="n"/>
+      <c r="Q290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -7997,6 +8454,7 @@
       <c r="N291" s="7" t="n"/>
       <c r="O291" s="7" t="n"/>
       <c r="P291" s="7" t="n"/>
+      <c r="Q291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -8015,6 +8473,7 @@
       <c r="N292" s="7" t="n"/>
       <c r="O292" s="7" t="n"/>
       <c r="P292" s="7" t="n"/>
+      <c r="Q292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -8033,6 +8492,7 @@
       <c r="N293" s="7" t="n"/>
       <c r="O293" s="7" t="n"/>
       <c r="P293" s="7" t="n"/>
+      <c r="Q293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -8051,6 +8511,7 @@
       <c r="N294" s="7" t="n"/>
       <c r="O294" s="7" t="n"/>
       <c r="P294" s="7" t="n"/>
+      <c r="Q294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -8069,6 +8530,7 @@
       <c r="N295" s="7" t="n"/>
       <c r="O295" s="7" t="n"/>
       <c r="P295" s="7" t="n"/>
+      <c r="Q295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -8087,6 +8549,7 @@
       <c r="N296" s="7" t="n"/>
       <c r="O296" s="7" t="n"/>
       <c r="P296" s="7" t="n"/>
+      <c r="Q296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -8105,6 +8568,7 @@
       <c r="N297" s="7" t="n"/>
       <c r="O297" s="7" t="n"/>
       <c r="P297" s="7" t="n"/>
+      <c r="Q297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -8123,6 +8587,7 @@
       <c r="N298" s="7" t="n"/>
       <c r="O298" s="7" t="n"/>
       <c r="P298" s="7" t="n"/>
+      <c r="Q298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -8141,6 +8606,7 @@
       <c r="N299" s="7" t="n"/>
       <c r="O299" s="7" t="n"/>
       <c r="P299" s="7" t="n"/>
+      <c r="Q299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -8159,6 +8625,7 @@
       <c r="N300" s="7" t="n"/>
       <c r="O300" s="7" t="n"/>
       <c r="P300" s="7" t="n"/>
+      <c r="Q300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -8177,6 +8644,7 @@
       <c r="N301" s="7" t="n"/>
       <c r="O301" s="7" t="n"/>
       <c r="P301" s="7" t="n"/>
+      <c r="Q301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -8195,6 +8663,7 @@
       <c r="N302" s="7" t="n"/>
       <c r="O302" s="7" t="n"/>
       <c r="P302" s="7" t="n"/>
+      <c r="Q302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -8213,6 +8682,7 @@
       <c r="N303" s="7" t="n"/>
       <c r="O303" s="7" t="n"/>
       <c r="P303" s="7" t="n"/>
+      <c r="Q303" s="7" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -8231,6 +8701,7 @@
       <c r="N304" s="7" t="n"/>
       <c r="O304" s="7" t="n"/>
       <c r="P304" s="7" t="n"/>
+      <c r="Q304" s="7" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -8249,6 +8720,7 @@
       <c r="N305" s="7" t="n"/>
       <c r="O305" s="7" t="n"/>
       <c r="P305" s="7" t="n"/>
+      <c r="Q305" s="7" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -8267,6 +8739,7 @@
       <c r="N306" s="7" t="n"/>
       <c r="O306" s="7" t="n"/>
       <c r="P306" s="7" t="n"/>
+      <c r="Q306" s="7" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -8285,6 +8758,7 @@
       <c r="N307" s="7" t="n"/>
       <c r="O307" s="7" t="n"/>
       <c r="P307" s="7" t="n"/>
+      <c r="Q307" s="7" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -8303,6 +8777,7 @@
       <c r="N308" s="7" t="n"/>
       <c r="O308" s="7" t="n"/>
       <c r="P308" s="7" t="n"/>
+      <c r="Q308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -8321,6 +8796,7 @@
       <c r="N309" s="7" t="n"/>
       <c r="O309" s="7" t="n"/>
       <c r="P309" s="7" t="n"/>
+      <c r="Q309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -8339,6 +8815,7 @@
       <c r="N310" s="7" t="n"/>
       <c r="O310" s="7" t="n"/>
       <c r="P310" s="7" t="n"/>
+      <c r="Q310" s="7" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -8357,6 +8834,7 @@
       <c r="N311" s="7" t="n"/>
       <c r="O311" s="7" t="n"/>
       <c r="P311" s="7" t="n"/>
+      <c r="Q311" s="7" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -8375,6 +8853,7 @@
       <c r="N312" s="7" t="n"/>
       <c r="O312" s="7" t="n"/>
       <c r="P312" s="7" t="n"/>
+      <c r="Q312" s="7" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -8393,6 +8872,7 @@
       <c r="N313" s="7" t="n"/>
       <c r="O313" s="7" t="n"/>
       <c r="P313" s="7" t="n"/>
+      <c r="Q313" s="7" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -8411,6 +8891,7 @@
       <c r="N314" s="7" t="n"/>
       <c r="O314" s="7" t="n"/>
       <c r="P314" s="7" t="n"/>
+      <c r="Q314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -8429,6 +8910,7 @@
       <c r="N315" s="7" t="n"/>
       <c r="O315" s="7" t="n"/>
       <c r="P315" s="7" t="n"/>
+      <c r="Q315" s="7" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -8447,6 +8929,7 @@
       <c r="N316" s="7" t="n"/>
       <c r="O316" s="7" t="n"/>
       <c r="P316" s="7" t="n"/>
+      <c r="Q316" s="7" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -8465,6 +8948,7 @@
       <c r="N317" s="7" t="n"/>
       <c r="O317" s="7" t="n"/>
       <c r="P317" s="7" t="n"/>
+      <c r="Q317" s="7" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -8483,6 +8967,7 @@
       <c r="N318" s="7" t="n"/>
       <c r="O318" s="7" t="n"/>
       <c r="P318" s="7" t="n"/>
+      <c r="Q318" s="7" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -8501,6 +8986,7 @@
       <c r="N319" s="7" t="n"/>
       <c r="O319" s="7" t="n"/>
       <c r="P319" s="7" t="n"/>
+      <c r="Q319" s="7" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -8519,6 +9005,7 @@
       <c r="N320" s="7" t="n"/>
       <c r="O320" s="7" t="n"/>
       <c r="P320" s="7" t="n"/>
+      <c r="Q320" s="7" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -8537,6 +9024,7 @@
       <c r="N321" s="7" t="n"/>
       <c r="O321" s="7" t="n"/>
       <c r="P321" s="7" t="n"/>
+      <c r="Q321" s="7" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -8555,6 +9043,7 @@
       <c r="N322" s="7" t="n"/>
       <c r="O322" s="7" t="n"/>
       <c r="P322" s="7" t="n"/>
+      <c r="Q322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -8573,6 +9062,7 @@
       <c r="N323" s="7" t="n"/>
       <c r="O323" s="7" t="n"/>
       <c r="P323" s="7" t="n"/>
+      <c r="Q323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -8591,6 +9081,7 @@
       <c r="N324" s="7" t="n"/>
       <c r="O324" s="7" t="n"/>
       <c r="P324" s="7" t="n"/>
+      <c r="Q324" s="7" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -8609,6 +9100,7 @@
       <c r="N325" s="7" t="n"/>
       <c r="O325" s="7" t="n"/>
       <c r="P325" s="7" t="n"/>
+      <c r="Q325" s="7" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -8627,6 +9119,7 @@
       <c r="N326" s="7" t="n"/>
       <c r="O326" s="7" t="n"/>
       <c r="P326" s="7" t="n"/>
+      <c r="Q326" s="7" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -8645,6 +9138,7 @@
       <c r="N327" s="7" t="n"/>
       <c r="O327" s="7" t="n"/>
       <c r="P327" s="7" t="n"/>
+      <c r="Q327" s="7" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -8663,6 +9157,7 @@
       <c r="N328" s="7" t="n"/>
       <c r="O328" s="7" t="n"/>
       <c r="P328" s="7" t="n"/>
+      <c r="Q328" s="7" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -8681,6 +9176,7 @@
       <c r="N329" s="7" t="n"/>
       <c r="O329" s="7" t="n"/>
       <c r="P329" s="7" t="n"/>
+      <c r="Q329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -8699,6 +9195,7 @@
       <c r="N330" s="7" t="n"/>
       <c r="O330" s="7" t="n"/>
       <c r="P330" s="7" t="n"/>
+      <c r="Q330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -8717,6 +9214,7 @@
       <c r="N331" s="7" t="n"/>
       <c r="O331" s="7" t="n"/>
       <c r="P331" s="7" t="n"/>
+      <c r="Q331" s="7" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -8735,6 +9233,7 @@
       <c r="N332" s="7" t="n"/>
       <c r="O332" s="7" t="n"/>
       <c r="P332" s="7" t="n"/>
+      <c r="Q332" s="7" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -8753,6 +9252,7 @@
       <c r="N333" s="7" t="n"/>
       <c r="O333" s="7" t="n"/>
       <c r="P333" s="7" t="n"/>
+      <c r="Q333" s="7" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -8771,6 +9271,7 @@
       <c r="N334" s="7" t="n"/>
       <c r="O334" s="7" t="n"/>
       <c r="P334" s="7" t="n"/>
+      <c r="Q334" s="7" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -8789,6 +9290,7 @@
       <c r="N335" s="7" t="n"/>
       <c r="O335" s="7" t="n"/>
       <c r="P335" s="7" t="n"/>
+      <c r="Q335" s="7" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -8807,6 +9309,7 @@
       <c r="N336" s="7" t="n"/>
       <c r="O336" s="7" t="n"/>
       <c r="P336" s="7" t="n"/>
+      <c r="Q336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -8825,6 +9328,7 @@
       <c r="N337" s="7" t="n"/>
       <c r="O337" s="7" t="n"/>
       <c r="P337" s="7" t="n"/>
+      <c r="Q337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -8843,6 +9347,7 @@
       <c r="N338" s="7" t="n"/>
       <c r="O338" s="7" t="n"/>
       <c r="P338" s="7" t="n"/>
+      <c r="Q338" s="7" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -8861,6 +9366,7 @@
       <c r="N339" s="7" t="n"/>
       <c r="O339" s="7" t="n"/>
       <c r="P339" s="7" t="n"/>
+      <c r="Q339" s="7" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -8879,6 +9385,7 @@
       <c r="N340" s="7" t="n"/>
       <c r="O340" s="7" t="n"/>
       <c r="P340" s="7" t="n"/>
+      <c r="Q340" s="7" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -8897,6 +9404,7 @@
       <c r="N341" s="7" t="n"/>
       <c r="O341" s="7" t="n"/>
       <c r="P341" s="7" t="n"/>
+      <c r="Q341" s="7" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -8915,6 +9423,7 @@
       <c r="N342" s="7" t="n"/>
       <c r="O342" s="7" t="n"/>
       <c r="P342" s="7" t="n"/>
+      <c r="Q342" s="7" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -8933,6 +9442,7 @@
       <c r="N343" s="7" t="n"/>
       <c r="O343" s="7" t="n"/>
       <c r="P343" s="7" t="n"/>
+      <c r="Q343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -8951,6 +9461,7 @@
       <c r="N344" s="7" t="n"/>
       <c r="O344" s="7" t="n"/>
       <c r="P344" s="7" t="n"/>
+      <c r="Q344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="7" t="n"/>
@@ -8969,6 +9480,7 @@
       <c r="N345" s="7" t="n"/>
       <c r="O345" s="7" t="n"/>
       <c r="P345" s="7" t="n"/>
+      <c r="Q345" s="7" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="7" t="n"/>
@@ -8987,6 +9499,7 @@
       <c r="N346" s="7" t="n"/>
       <c r="O346" s="7" t="n"/>
       <c r="P346" s="7" t="n"/>
+      <c r="Q346" s="7" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="7" t="n"/>
@@ -9005,6 +9518,7 @@
       <c r="N347" s="7" t="n"/>
       <c r="O347" s="7" t="n"/>
       <c r="P347" s="7" t="n"/>
+      <c r="Q347" s="7" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -9023,6 +9537,7 @@
       <c r="N348" s="7" t="n"/>
       <c r="O348" s="7" t="n"/>
       <c r="P348" s="7" t="n"/>
+      <c r="Q348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -9041,6 +9556,7 @@
       <c r="N349" s="7" t="n"/>
       <c r="O349" s="7" t="n"/>
       <c r="P349" s="7" t="n"/>
+      <c r="Q349" s="7" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -9059,6 +9575,7 @@
       <c r="N350" s="7" t="n"/>
       <c r="O350" s="7" t="n"/>
       <c r="P350" s="7" t="n"/>
+      <c r="Q350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -9077,6 +9594,7 @@
       <c r="N351" s="7" t="n"/>
       <c r="O351" s="7" t="n"/>
       <c r="P351" s="7" t="n"/>
+      <c r="Q351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -9095,6 +9613,7 @@
       <c r="N352" s="7" t="n"/>
       <c r="O352" s="7" t="n"/>
       <c r="P352" s="7" t="n"/>
+      <c r="Q352" s="7" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -9113,6 +9632,7 @@
       <c r="N353" s="7" t="n"/>
       <c r="O353" s="7" t="n"/>
       <c r="P353" s="7" t="n"/>
+      <c r="Q353" s="7" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -9131,6 +9651,7 @@
       <c r="N354" s="7" t="n"/>
       <c r="O354" s="7" t="n"/>
       <c r="P354" s="7" t="n"/>
+      <c r="Q354" s="7" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -9149,6 +9670,7 @@
       <c r="N355" s="7" t="n"/>
       <c r="O355" s="7" t="n"/>
       <c r="P355" s="7" t="n"/>
+      <c r="Q355" s="7" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -9167,6 +9689,7 @@
       <c r="N356" s="7" t="n"/>
       <c r="O356" s="7" t="n"/>
       <c r="P356" s="7" t="n"/>
+      <c r="Q356" s="7" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -9185,6 +9708,7 @@
       <c r="N357" s="7" t="n"/>
       <c r="O357" s="7" t="n"/>
       <c r="P357" s="7" t="n"/>
+      <c r="Q357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -9203,6 +9727,7 @@
       <c r="N358" s="7" t="n"/>
       <c r="O358" s="7" t="n"/>
       <c r="P358" s="7" t="n"/>
+      <c r="Q358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -9221,6 +9746,7 @@
       <c r="N359" s="7" t="n"/>
       <c r="O359" s="7" t="n"/>
       <c r="P359" s="7" t="n"/>
+      <c r="Q359" s="7" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -9239,6 +9765,7 @@
       <c r="N360" s="7" t="n"/>
       <c r="O360" s="7" t="n"/>
       <c r="P360" s="7" t="n"/>
+      <c r="Q360" s="7" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -9257,6 +9784,7 @@
       <c r="N361" s="7" t="n"/>
       <c r="O361" s="7" t="n"/>
       <c r="P361" s="7" t="n"/>
+      <c r="Q361" s="7" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -9275,6 +9803,7 @@
       <c r="N362" s="7" t="n"/>
       <c r="O362" s="7" t="n"/>
       <c r="P362" s="7" t="n"/>
+      <c r="Q362" s="7" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -9293,6 +9822,7 @@
       <c r="N363" s="7" t="n"/>
       <c r="O363" s="7" t="n"/>
       <c r="P363" s="7" t="n"/>
+      <c r="Q363" s="7" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -9311,6 +9841,7 @@
       <c r="N364" s="7" t="n"/>
       <c r="O364" s="7" t="n"/>
       <c r="P364" s="7" t="n"/>
+      <c r="Q364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -9329,6 +9860,7 @@
       <c r="N365" s="7" t="n"/>
       <c r="O365" s="7" t="n"/>
       <c r="P365" s="7" t="n"/>
+      <c r="Q365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -9347,6 +9879,7 @@
       <c r="N366" s="7" t="n"/>
       <c r="O366" s="7" t="n"/>
       <c r="P366" s="7" t="n"/>
+      <c r="Q366" s="7" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -9365,6 +9898,7 @@
       <c r="N367" s="7" t="n"/>
       <c r="O367" s="7" t="n"/>
       <c r="P367" s="7" t="n"/>
+      <c r="Q367" s="7" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -9383,6 +9917,7 @@
       <c r="N368" s="7" t="n"/>
       <c r="O368" s="7" t="n"/>
       <c r="P368" s="7" t="n"/>
+      <c r="Q368" s="7" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -9401,6 +9936,7 @@
       <c r="N369" s="7" t="n"/>
       <c r="O369" s="7" t="n"/>
       <c r="P369" s="7" t="n"/>
+      <c r="Q369" s="7" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -9419,6 +9955,7 @@
       <c r="N370" s="7" t="n"/>
       <c r="O370" s="7" t="n"/>
       <c r="P370" s="7" t="n"/>
+      <c r="Q370" s="7" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -9437,6 +9974,7 @@
       <c r="N371" s="7" t="n"/>
       <c r="O371" s="7" t="n"/>
       <c r="P371" s="7" t="n"/>
+      <c r="Q371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -9455,6 +9993,7 @@
       <c r="N372" s="7" t="n"/>
       <c r="O372" s="7" t="n"/>
       <c r="P372" s="7" t="n"/>
+      <c r="Q372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -9473,6 +10012,7 @@
       <c r="N373" s="7" t="n"/>
       <c r="O373" s="7" t="n"/>
       <c r="P373" s="7" t="n"/>
+      <c r="Q373" s="7" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -9491,6 +10031,7 @@
       <c r="N374" s="7" t="n"/>
       <c r="O374" s="7" t="n"/>
       <c r="P374" s="7" t="n"/>
+      <c r="Q374" s="7" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -9509,6 +10050,7 @@
       <c r="N375" s="7" t="n"/>
       <c r="O375" s="7" t="n"/>
       <c r="P375" s="7" t="n"/>
+      <c r="Q375" s="7" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -9527,6 +10069,7 @@
       <c r="N376" s="7" t="n"/>
       <c r="O376" s="7" t="n"/>
       <c r="P376" s="7" t="n"/>
+      <c r="Q376" s="7" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -9545,6 +10088,7 @@
       <c r="N377" s="7" t="n"/>
       <c r="O377" s="7" t="n"/>
       <c r="P377" s="7" t="n"/>
+      <c r="Q377" s="7" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -9563,6 +10107,7 @@
       <c r="N378" s="7" t="n"/>
       <c r="O378" s="7" t="n"/>
       <c r="P378" s="7" t="n"/>
+      <c r="Q378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -9581,6 +10126,7 @@
       <c r="N379" s="7" t="n"/>
       <c r="O379" s="7" t="n"/>
       <c r="P379" s="7" t="n"/>
+      <c r="Q379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -9599,6 +10145,7 @@
       <c r="N380" s="7" t="n"/>
       <c r="O380" s="7" t="n"/>
       <c r="P380" s="7" t="n"/>
+      <c r="Q380" s="7" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -9617,6 +10164,7 @@
       <c r="N381" s="7" t="n"/>
       <c r="O381" s="7" t="n"/>
       <c r="P381" s="7" t="n"/>
+      <c r="Q381" s="7" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -9635,6 +10183,7 @@
       <c r="N382" s="7" t="n"/>
       <c r="O382" s="7" t="n"/>
       <c r="P382" s="7" t="n"/>
+      <c r="Q382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -9653,6 +10202,7 @@
       <c r="N383" s="7" t="n"/>
       <c r="O383" s="7" t="n"/>
       <c r="P383" s="7" t="n"/>
+      <c r="Q383" s="7" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -9671,6 +10221,7 @@
       <c r="N384" s="7" t="n"/>
       <c r="O384" s="7" t="n"/>
       <c r="P384" s="7" t="n"/>
+      <c r="Q384" s="7" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -9689,6 +10240,7 @@
       <c r="N385" s="7" t="n"/>
       <c r="O385" s="7" t="n"/>
       <c r="P385" s="7" t="n"/>
+      <c r="Q385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -9707,6 +10259,7 @@
       <c r="N386" s="7" t="n"/>
       <c r="O386" s="7" t="n"/>
       <c r="P386" s="7" t="n"/>
+      <c r="Q386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -9725,6 +10278,7 @@
       <c r="N387" s="7" t="n"/>
       <c r="O387" s="7" t="n"/>
       <c r="P387" s="7" t="n"/>
+      <c r="Q387" s="7" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -9743,6 +10297,7 @@
       <c r="N388" s="7" t="n"/>
       <c r="O388" s="7" t="n"/>
       <c r="P388" s="7" t="n"/>
+      <c r="Q388" s="7" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -9761,6 +10316,7 @@
       <c r="N389" s="7" t="n"/>
       <c r="O389" s="7" t="n"/>
       <c r="P389" s="7" t="n"/>
+      <c r="Q389" s="7" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -9779,6 +10335,7 @@
       <c r="N390" s="7" t="n"/>
       <c r="O390" s="7" t="n"/>
       <c r="P390" s="7" t="n"/>
+      <c r="Q390" s="7" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -9797,6 +10354,7 @@
       <c r="N391" s="7" t="n"/>
       <c r="O391" s="7" t="n"/>
       <c r="P391" s="7" t="n"/>
+      <c r="Q391" s="7" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -9815,6 +10373,7 @@
       <c r="N392" s="7" t="n"/>
       <c r="O392" s="7" t="n"/>
       <c r="P392" s="7" t="n"/>
+      <c r="Q392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -9833,6 +10392,7 @@
       <c r="N393" s="7" t="n"/>
       <c r="O393" s="7" t="n"/>
       <c r="P393" s="7" t="n"/>
+      <c r="Q393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -9851,6 +10411,7 @@
       <c r="N394" s="7" t="n"/>
       <c r="O394" s="7" t="n"/>
       <c r="P394" s="7" t="n"/>
+      <c r="Q394" s="7" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -9869,6 +10430,7 @@
       <c r="N395" s="7" t="n"/>
       <c r="O395" s="7" t="n"/>
       <c r="P395" s="7" t="n"/>
+      <c r="Q395" s="7" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -9887,6 +10449,7 @@
       <c r="N396" s="7" t="n"/>
       <c r="O396" s="7" t="n"/>
       <c r="P396" s="7" t="n"/>
+      <c r="Q396" s="7" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -9905,6 +10468,7 @@
       <c r="N397" s="7" t="n"/>
       <c r="O397" s="7" t="n"/>
       <c r="P397" s="7" t="n"/>
+      <c r="Q397" s="7" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -9923,6 +10487,7 @@
       <c r="N398" s="7" t="n"/>
       <c r="O398" s="7" t="n"/>
       <c r="P398" s="7" t="n"/>
+      <c r="Q398" s="7" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -9941,6 +10506,7 @@
       <c r="N399" s="7" t="n"/>
       <c r="O399" s="7" t="n"/>
       <c r="P399" s="7" t="n"/>
+      <c r="Q399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -9959,6 +10525,7 @@
       <c r="N400" s="7" t="n"/>
       <c r="O400" s="7" t="n"/>
       <c r="P400" s="7" t="n"/>
+      <c r="Q400" s="7" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="7" t="n"/>
@@ -9977,6 +10544,7 @@
       <c r="N401" s="7" t="n"/>
       <c r="O401" s="7" t="n"/>
       <c r="P401" s="7" t="n"/>
+      <c r="Q401" s="7" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="7" t="n"/>
@@ -9995,6 +10563,7 @@
       <c r="N402" s="7" t="n"/>
       <c r="O402" s="7" t="n"/>
       <c r="P402" s="7" t="n"/>
+      <c r="Q402" s="7" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="7" t="n"/>
@@ -10013,6 +10582,7 @@
       <c r="N403" s="7" t="n"/>
       <c r="O403" s="7" t="n"/>
       <c r="P403" s="7" t="n"/>
+      <c r="Q403" s="7" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="7" t="n"/>
@@ -10031,6 +10601,7 @@
       <c r="N404" s="7" t="n"/>
       <c r="O404" s="7" t="n"/>
       <c r="P404" s="7" t="n"/>
+      <c r="Q404" s="7" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="7" t="n"/>
@@ -10049,6 +10620,7 @@
       <c r="N405" s="7" t="n"/>
       <c r="O405" s="7" t="n"/>
       <c r="P405" s="7" t="n"/>
+      <c r="Q405" s="7" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="7" t="n"/>
@@ -10067,6 +10639,7 @@
       <c r="N406" s="7" t="n"/>
       <c r="O406" s="7" t="n"/>
       <c r="P406" s="7" t="n"/>
+      <c r="Q406" s="7" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="7" t="n"/>
@@ -10085,6 +10658,7 @@
       <c r="N407" s="7" t="n"/>
       <c r="O407" s="7" t="n"/>
       <c r="P407" s="7" t="n"/>
+      <c r="Q407" s="7" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="7" t="n"/>
@@ -10103,6 +10677,7 @@
       <c r="N408" s="7" t="n"/>
       <c r="O408" s="7" t="n"/>
       <c r="P408" s="7" t="n"/>
+      <c r="Q408" s="7" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="7" t="n"/>
@@ -10121,6 +10696,7 @@
       <c r="N409" s="7" t="n"/>
       <c r="O409" s="7" t="n"/>
       <c r="P409" s="7" t="n"/>
+      <c r="Q409" s="7" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="7" t="n"/>
@@ -10139,6 +10715,7 @@
       <c r="N410" s="7" t="n"/>
       <c r="O410" s="7" t="n"/>
       <c r="P410" s="7" t="n"/>
+      <c r="Q410" s="7" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="7" t="n"/>
@@ -10157,6 +10734,7 @@
       <c r="N411" s="7" t="n"/>
       <c r="O411" s="7" t="n"/>
       <c r="P411" s="7" t="n"/>
+      <c r="Q411" s="7" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="7" t="n"/>
@@ -10175,6 +10753,7 @@
       <c r="N412" s="7" t="n"/>
       <c r="O412" s="7" t="n"/>
       <c r="P412" s="7" t="n"/>
+      <c r="Q412" s="7" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="7" t="n"/>
@@ -10193,6 +10772,7 @@
       <c r="N413" s="7" t="n"/>
       <c r="O413" s="7" t="n"/>
       <c r="P413" s="7" t="n"/>
+      <c r="Q413" s="7" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="7" t="n"/>
@@ -10211,6 +10791,7 @@
       <c r="N414" s="7" t="n"/>
       <c r="O414" s="7" t="n"/>
       <c r="P414" s="7" t="n"/>
+      <c r="Q414" s="7" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="7" t="n"/>
@@ -10229,6 +10810,7 @@
       <c r="N415" s="7" t="n"/>
       <c r="O415" s="7" t="n"/>
       <c r="P415" s="7" t="n"/>
+      <c r="Q415" s="7" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="7" t="n"/>
@@ -10247,6 +10829,7 @@
       <c r="N416" s="7" t="n"/>
       <c r="O416" s="7" t="n"/>
       <c r="P416" s="7" t="n"/>
+      <c r="Q416" s="7" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="7" t="n"/>
@@ -10265,6 +10848,7 @@
       <c r="N417" s="7" t="n"/>
       <c r="O417" s="7" t="n"/>
       <c r="P417" s="7" t="n"/>
+      <c r="Q417" s="7" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="7" t="n"/>
@@ -10283,6 +10867,7 @@
       <c r="N418" s="7" t="n"/>
       <c r="O418" s="7" t="n"/>
       <c r="P418" s="7" t="n"/>
+      <c r="Q418" s="7" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="7" t="n"/>
@@ -10301,6 +10886,7 @@
       <c r="N419" s="7" t="n"/>
       <c r="O419" s="7" t="n"/>
       <c r="P419" s="7" t="n"/>
+      <c r="Q419" s="7" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="7" t="n"/>
@@ -10319,6 +10905,7 @@
       <c r="N420" s="7" t="n"/>
       <c r="O420" s="7" t="n"/>
       <c r="P420" s="7" t="n"/>
+      <c r="Q420" s="7" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="7" t="n"/>
@@ -10337,6 +10924,7 @@
       <c r="N421" s="7" t="n"/>
       <c r="O421" s="7" t="n"/>
       <c r="P421" s="7" t="n"/>
+      <c r="Q421" s="7" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="7" t="n"/>
@@ -10355,6 +10943,7 @@
       <c r="N422" s="7" t="n"/>
       <c r="O422" s="7" t="n"/>
       <c r="P422" s="7" t="n"/>
+      <c r="Q422" s="7" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="7" t="n"/>
@@ -10373,6 +10962,7 @@
       <c r="N423" s="7" t="n"/>
       <c r="O423" s="7" t="n"/>
       <c r="P423" s="7" t="n"/>
+      <c r="Q423" s="7" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="7" t="n"/>
@@ -10391,6 +10981,7 @@
       <c r="N424" s="7" t="n"/>
       <c r="O424" s="7" t="n"/>
       <c r="P424" s="7" t="n"/>
+      <c r="Q424" s="7" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="7" t="n"/>
@@ -10409,6 +11000,7 @@
       <c r="N425" s="7" t="n"/>
       <c r="O425" s="7" t="n"/>
       <c r="P425" s="7" t="n"/>
+      <c r="Q425" s="7" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="7" t="n"/>
@@ -10427,6 +11019,7 @@
       <c r="N426" s="7" t="n"/>
       <c r="O426" s="7" t="n"/>
       <c r="P426" s="7" t="n"/>
+      <c r="Q426" s="7" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="7" t="n"/>
@@ -10445,6 +11038,7 @@
       <c r="N427" s="7" t="n"/>
       <c r="O427" s="7" t="n"/>
       <c r="P427" s="7" t="n"/>
+      <c r="Q427" s="7" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="7" t="n"/>
@@ -10463,6 +11057,7 @@
       <c r="N428" s="7" t="n"/>
       <c r="O428" s="7" t="n"/>
       <c r="P428" s="7" t="n"/>
+      <c r="Q428" s="7" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="7" t="n"/>
@@ -10481,6 +11076,7 @@
       <c r="N429" s="7" t="n"/>
       <c r="O429" s="7" t="n"/>
       <c r="P429" s="7" t="n"/>
+      <c r="Q429" s="7" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="7" t="n"/>
@@ -10499,6 +11095,7 @@
       <c r="N430" s="7" t="n"/>
       <c r="O430" s="7" t="n"/>
       <c r="P430" s="7" t="n"/>
+      <c r="Q430" s="7" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="7" t="n"/>
@@ -10517,6 +11114,7 @@
       <c r="N431" s="7" t="n"/>
       <c r="O431" s="7" t="n"/>
       <c r="P431" s="7" t="n"/>
+      <c r="Q431" s="7" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="7" t="n"/>
@@ -10535,6 +11133,7 @@
       <c r="N432" s="7" t="n"/>
       <c r="O432" s="7" t="n"/>
       <c r="P432" s="7" t="n"/>
+      <c r="Q432" s="7" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="7" t="n"/>
@@ -10553,6 +11152,7 @@
       <c r="N433" s="7" t="n"/>
       <c r="O433" s="7" t="n"/>
       <c r="P433" s="7" t="n"/>
+      <c r="Q433" s="7" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="7" t="n"/>
@@ -10571,6 +11171,7 @@
       <c r="N434" s="7" t="n"/>
       <c r="O434" s="7" t="n"/>
       <c r="P434" s="7" t="n"/>
+      <c r="Q434" s="7" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="7" t="n"/>
@@ -10589,6 +11190,7 @@
       <c r="N435" s="7" t="n"/>
       <c r="O435" s="7" t="n"/>
       <c r="P435" s="7" t="n"/>
+      <c r="Q435" s="7" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="7" t="n"/>
@@ -10607,6 +11209,7 @@
       <c r="N436" s="7" t="n"/>
       <c r="O436" s="7" t="n"/>
       <c r="P436" s="7" t="n"/>
+      <c r="Q436" s="7" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="7" t="n"/>
@@ -10625,6 +11228,7 @@
       <c r="N437" s="7" t="n"/>
       <c r="O437" s="7" t="n"/>
       <c r="P437" s="7" t="n"/>
+      <c r="Q437" s="7" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="7" t="n"/>
@@ -10643,6 +11247,7 @@
       <c r="N438" s="7" t="n"/>
       <c r="O438" s="7" t="n"/>
       <c r="P438" s="7" t="n"/>
+      <c r="Q438" s="7" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="7" t="n"/>
@@ -10661,6 +11266,7 @@
       <c r="N439" s="7" t="n"/>
       <c r="O439" s="7" t="n"/>
       <c r="P439" s="7" t="n"/>
+      <c r="Q439" s="7" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="7" t="n"/>
@@ -10679,6 +11285,7 @@
       <c r="N440" s="7" t="n"/>
       <c r="O440" s="7" t="n"/>
       <c r="P440" s="7" t="n"/>
+      <c r="Q440" s="7" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="7" t="n"/>
@@ -10697,6 +11304,7 @@
       <c r="N441" s="7" t="n"/>
       <c r="O441" s="7" t="n"/>
       <c r="P441" s="7" t="n"/>
+      <c r="Q441" s="7" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="7" t="n"/>
@@ -10715,6 +11323,7 @@
       <c r="N442" s="7" t="n"/>
       <c r="O442" s="7" t="n"/>
       <c r="P442" s="7" t="n"/>
+      <c r="Q442" s="7" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="7" t="n"/>
@@ -10733,6 +11342,7 @@
       <c r="N443" s="7" t="n"/>
       <c r="O443" s="7" t="n"/>
       <c r="P443" s="7" t="n"/>
+      <c r="Q443" s="7" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="7" t="n"/>
@@ -10751,6 +11361,7 @@
       <c r="N444" s="7" t="n"/>
       <c r="O444" s="7" t="n"/>
       <c r="P444" s="7" t="n"/>
+      <c r="Q444" s="7" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="7" t="n"/>
@@ -10769,6 +11380,7 @@
       <c r="N445" s="7" t="n"/>
       <c r="O445" s="7" t="n"/>
       <c r="P445" s="7" t="n"/>
+      <c r="Q445" s="7" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="7" t="n"/>
@@ -10787,6 +11399,7 @@
       <c r="N446" s="7" t="n"/>
       <c r="O446" s="7" t="n"/>
       <c r="P446" s="7" t="n"/>
+      <c r="Q446" s="7" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="7" t="n"/>
@@ -10805,6 +11418,7 @@
       <c r="N447" s="7" t="n"/>
       <c r="O447" s="7" t="n"/>
       <c r="P447" s="7" t="n"/>
+      <c r="Q447" s="7" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="7" t="n"/>
@@ -10823,6 +11437,7 @@
       <c r="N448" s="7" t="n"/>
       <c r="O448" s="7" t="n"/>
       <c r="P448" s="7" t="n"/>
+      <c r="Q448" s="7" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="7" t="n"/>
@@ -10841,6 +11456,7 @@
       <c r="N449" s="7" t="n"/>
       <c r="O449" s="7" t="n"/>
       <c r="P449" s="7" t="n"/>
+      <c r="Q449" s="7" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="7" t="n"/>
@@ -10859,6 +11475,7 @@
       <c r="N450" s="7" t="n"/>
       <c r="O450" s="7" t="n"/>
       <c r="P450" s="7" t="n"/>
+      <c r="Q450" s="7" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="7" t="n"/>
@@ -10877,6 +11494,7 @@
       <c r="N451" s="7" t="n"/>
       <c r="O451" s="7" t="n"/>
       <c r="P451" s="7" t="n"/>
+      <c r="Q451" s="7" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="7" t="n"/>
@@ -10895,6 +11513,7 @@
       <c r="N452" s="7" t="n"/>
       <c r="O452" s="7" t="n"/>
       <c r="P452" s="7" t="n"/>
+      <c r="Q452" s="7" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="7" t="n"/>
@@ -10913,6 +11532,7 @@
       <c r="N453" s="7" t="n"/>
       <c r="O453" s="7" t="n"/>
       <c r="P453" s="7" t="n"/>
+      <c r="Q453" s="7" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="7" t="n"/>
@@ -10931,6 +11551,7 @@
       <c r="N454" s="7" t="n"/>
       <c r="O454" s="7" t="n"/>
       <c r="P454" s="7" t="n"/>
+      <c r="Q454" s="7" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="7" t="n"/>
@@ -10949,6 +11570,7 @@
       <c r="N455" s="7" t="n"/>
       <c r="O455" s="7" t="n"/>
       <c r="P455" s="7" t="n"/>
+      <c r="Q455" s="7" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="7" t="n"/>
@@ -10967,6 +11589,7 @@
       <c r="N456" s="7" t="n"/>
       <c r="O456" s="7" t="n"/>
       <c r="P456" s="7" t="n"/>
+      <c r="Q456" s="7" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="7" t="n"/>
@@ -10985,6 +11608,7 @@
       <c r="N457" s="7" t="n"/>
       <c r="O457" s="7" t="n"/>
       <c r="P457" s="7" t="n"/>
+      <c r="Q457" s="7" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="7" t="n"/>
@@ -11003,6 +11627,7 @@
       <c r="N458" s="7" t="n"/>
       <c r="O458" s="7" t="n"/>
       <c r="P458" s="7" t="n"/>
+      <c r="Q458" s="7" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="7" t="n"/>
@@ -11021,6 +11646,7 @@
       <c r="N459" s="7" t="n"/>
       <c r="O459" s="7" t="n"/>
       <c r="P459" s="7" t="n"/>
+      <c r="Q459" s="7" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="7" t="n"/>
@@ -11039,6 +11665,7 @@
       <c r="N460" s="7" t="n"/>
       <c r="O460" s="7" t="n"/>
       <c r="P460" s="7" t="n"/>
+      <c r="Q460" s="7" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="7" t="n"/>
@@ -11057,6 +11684,7 @@
       <c r="N461" s="7" t="n"/>
       <c r="O461" s="7" t="n"/>
       <c r="P461" s="7" t="n"/>
+      <c r="Q461" s="7" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="7" t="n"/>
@@ -11075,6 +11703,7 @@
       <c r="N462" s="7" t="n"/>
       <c r="O462" s="7" t="n"/>
       <c r="P462" s="7" t="n"/>
+      <c r="Q462" s="7" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="7" t="n"/>
@@ -11093,6 +11722,7 @@
       <c r="N463" s="7" t="n"/>
       <c r="O463" s="7" t="n"/>
       <c r="P463" s="7" t="n"/>
+      <c r="Q463" s="7" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="7" t="n"/>
@@ -11111,6 +11741,7 @@
       <c r="N464" s="7" t="n"/>
       <c r="O464" s="7" t="n"/>
       <c r="P464" s="7" t="n"/>
+      <c r="Q464" s="7" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="7" t="n"/>
@@ -11129,6 +11760,7 @@
       <c r="N465" s="7" t="n"/>
       <c r="O465" s="7" t="n"/>
       <c r="P465" s="7" t="n"/>
+      <c r="Q465" s="7" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="7" t="n"/>
@@ -11147,6 +11779,7 @@
       <c r="N466" s="7" t="n"/>
       <c r="O466" s="7" t="n"/>
       <c r="P466" s="7" t="n"/>
+      <c r="Q466" s="7" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="7" t="n"/>
@@ -11165,6 +11798,7 @@
       <c r="N467" s="7" t="n"/>
       <c r="O467" s="7" t="n"/>
       <c r="P467" s="7" t="n"/>
+      <c r="Q467" s="7" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="7" t="n"/>
@@ -11183,6 +11817,7 @@
       <c r="N468" s="7" t="n"/>
       <c r="O468" s="7" t="n"/>
       <c r="P468" s="7" t="n"/>
+      <c r="Q468" s="7" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="7" t="n"/>
@@ -11201,6 +11836,7 @@
       <c r="N469" s="7" t="n"/>
       <c r="O469" s="7" t="n"/>
       <c r="P469" s="7" t="n"/>
+      <c r="Q469" s="7" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="7" t="n"/>
@@ -11219,6 +11855,7 @@
       <c r="N470" s="7" t="n"/>
       <c r="O470" s="7" t="n"/>
       <c r="P470" s="7" t="n"/>
+      <c r="Q470" s="7" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="7" t="n"/>
@@ -11237,6 +11874,7 @@
       <c r="N471" s="7" t="n"/>
       <c r="O471" s="7" t="n"/>
       <c r="P471" s="7" t="n"/>
+      <c r="Q471" s="7" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="7" t="n"/>
@@ -11255,6 +11893,7 @@
       <c r="N472" s="7" t="n"/>
       <c r="O472" s="7" t="n"/>
       <c r="P472" s="7" t="n"/>
+      <c r="Q472" s="7" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="7" t="n"/>
@@ -11273,6 +11912,7 @@
       <c r="N473" s="7" t="n"/>
       <c r="O473" s="7" t="n"/>
       <c r="P473" s="7" t="n"/>
+      <c r="Q473" s="7" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="7" t="n"/>
@@ -11291,6 +11931,7 @@
       <c r="N474" s="7" t="n"/>
       <c r="O474" s="7" t="n"/>
       <c r="P474" s="7" t="n"/>
+      <c r="Q474" s="7" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="7" t="n"/>
@@ -11309,6 +11950,7 @@
       <c r="N475" s="7" t="n"/>
       <c r="O475" s="7" t="n"/>
       <c r="P475" s="7" t="n"/>
+      <c r="Q475" s="7" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="7" t="n"/>
@@ -11327,6 +11969,7 @@
       <c r="N476" s="7" t="n"/>
       <c r="O476" s="7" t="n"/>
       <c r="P476" s="7" t="n"/>
+      <c r="Q476" s="7" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="7" t="n"/>
@@ -11345,6 +11988,7 @@
       <c r="N477" s="7" t="n"/>
       <c r="O477" s="7" t="n"/>
       <c r="P477" s="7" t="n"/>
+      <c r="Q477" s="7" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="7" t="n"/>
@@ -11363,6 +12007,7 @@
       <c r="N478" s="7" t="n"/>
       <c r="O478" s="7" t="n"/>
       <c r="P478" s="7" t="n"/>
+      <c r="Q478" s="7" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="7" t="n"/>
@@ -11381,6 +12026,7 @@
       <c r="N479" s="7" t="n"/>
       <c r="O479" s="7" t="n"/>
       <c r="P479" s="7" t="n"/>
+      <c r="Q479" s="7" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="7" t="n"/>
@@ -11399,6 +12045,7 @@
       <c r="N480" s="7" t="n"/>
       <c r="O480" s="7" t="n"/>
       <c r="P480" s="7" t="n"/>
+      <c r="Q480" s="7" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="7" t="n"/>
@@ -11417,6 +12064,7 @@
       <c r="N481" s="7" t="n"/>
       <c r="O481" s="7" t="n"/>
       <c r="P481" s="7" t="n"/>
+      <c r="Q481" s="7" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="7" t="n"/>
@@ -11435,6 +12083,7 @@
       <c r="N482" s="7" t="n"/>
       <c r="O482" s="7" t="n"/>
       <c r="P482" s="7" t="n"/>
+      <c r="Q482" s="7" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="7" t="n"/>
@@ -11453,6 +12102,7 @@
       <c r="N483" s="7" t="n"/>
       <c r="O483" s="7" t="n"/>
       <c r="P483" s="7" t="n"/>
+      <c r="Q483" s="7" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="7" t="n"/>
@@ -11471,6 +12121,7 @@
       <c r="N484" s="7" t="n"/>
       <c r="O484" s="7" t="n"/>
       <c r="P484" s="7" t="n"/>
+      <c r="Q484" s="7" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="7" t="n"/>
@@ -11489,6 +12140,7 @@
       <c r="N485" s="7" t="n"/>
       <c r="O485" s="7" t="n"/>
       <c r="P485" s="7" t="n"/>
+      <c r="Q485" s="7" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="7" t="n"/>
@@ -11507,6 +12159,7 @@
       <c r="N486" s="7" t="n"/>
       <c r="O486" s="7" t="n"/>
       <c r="P486" s="7" t="n"/>
+      <c r="Q486" s="7" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="7" t="n"/>
@@ -11525,6 +12178,7 @@
       <c r="N487" s="7" t="n"/>
       <c r="O487" s="7" t="n"/>
       <c r="P487" s="7" t="n"/>
+      <c r="Q487" s="7" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="7" t="n"/>
@@ -11543,6 +12197,7 @@
       <c r="N488" s="7" t="n"/>
       <c r="O488" s="7" t="n"/>
       <c r="P488" s="7" t="n"/>
+      <c r="Q488" s="7" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="7" t="n"/>
@@ -11561,6 +12216,7 @@
       <c r="N489" s="7" t="n"/>
       <c r="O489" s="7" t="n"/>
       <c r="P489" s="7" t="n"/>
+      <c r="Q489" s="7" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="7" t="n"/>
@@ -11579,6 +12235,7 @@
       <c r="N490" s="7" t="n"/>
       <c r="O490" s="7" t="n"/>
       <c r="P490" s="7" t="n"/>
+      <c r="Q490" s="7" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="7" t="n"/>
@@ -11597,6 +12254,7 @@
       <c r="N491" s="7" t="n"/>
       <c r="O491" s="7" t="n"/>
       <c r="P491" s="7" t="n"/>
+      <c r="Q491" s="7" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="7" t="n"/>
@@ -11615,6 +12273,7 @@
       <c r="N492" s="7" t="n"/>
       <c r="O492" s="7" t="n"/>
       <c r="P492" s="7" t="n"/>
+      <c r="Q492" s="7" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="7" t="n"/>
@@ -11633,6 +12292,7 @@
       <c r="N493" s="7" t="n"/>
       <c r="O493" s="7" t="n"/>
       <c r="P493" s="7" t="n"/>
+      <c r="Q493" s="7" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="7" t="n"/>
@@ -11651,6 +12311,7 @@
       <c r="N494" s="7" t="n"/>
       <c r="O494" s="7" t="n"/>
       <c r="P494" s="7" t="n"/>
+      <c r="Q494" s="7" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="7" t="n"/>
@@ -11669,6 +12330,7 @@
       <c r="N495" s="7" t="n"/>
       <c r="O495" s="7" t="n"/>
       <c r="P495" s="7" t="n"/>
+      <c r="Q495" s="7" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="7" t="n"/>
@@ -11687,6 +12349,7 @@
       <c r="N496" s="7" t="n"/>
       <c r="O496" s="7" t="n"/>
       <c r="P496" s="7" t="n"/>
+      <c r="Q496" s="7" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="7" t="n"/>
@@ -11705,6 +12368,7 @@
       <c r="N497" s="7" t="n"/>
       <c r="O497" s="7" t="n"/>
       <c r="P497" s="7" t="n"/>
+      <c r="Q497" s="7" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="7" t="n"/>
@@ -11723,6 +12387,7 @@
       <c r="N498" s="7" t="n"/>
       <c r="O498" s="7" t="n"/>
       <c r="P498" s="7" t="n"/>
+      <c r="Q498" s="7" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="7" t="n"/>
@@ -11741,6 +12406,7 @@
       <c r="N499" s="7" t="n"/>
       <c r="O499" s="7" t="n"/>
       <c r="P499" s="7" t="n"/>
+      <c r="Q499" s="7" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="7" t="n"/>
@@ -11759,25 +12425,26 @@
       <c r="N500" s="7" t="n"/>
       <c r="O500" s="7" t="n"/>
       <c r="P500" s="7" t="n"/>
+      <c r="Q500" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P500"/>
-  <conditionalFormatting sqref="A2:P500">
+  <autoFilter ref="A1:Q500"/>
+  <conditionalFormatting sqref="A2:Q500">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$G2="нет"</formula>
+      <formula>$H2="нет"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Справочники!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Справочники!$B$2:$B$30</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Справочники!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Справочники!$A$2:$A$3</formula1>
     </dataValidation>
   </dataValidations>
